--- a/data/SEMANA ATUAL/rodada 8/COLEIRAS.xlsx
+++ b/data/SEMANA ATUAL/rodada 8/COLEIRAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="280">
   <si>
     <t>Sigla Loja</t>
   </si>
@@ -32,6 +32,15 @@
   </si>
   <si>
     <t>20/08/2026 (Qui)</t>
+  </si>
+  <si>
+    <t>21/08/2026 (Sex)</t>
+  </si>
+  <si>
+    <t>22/08/2026 (Sáb)</t>
+  </si>
+  <si>
+    <t>23/08/2026 (Dom)</t>
   </si>
   <si>
     <t>ABNO-RJ</t>
@@ -1210,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F271"/>
+  <dimension ref="A1:I271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1218,7 +1227,7 @@
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1237,10 +1246,19 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>694.96</v>
@@ -1254,13 +1272,22 @@
       <c r="F2" s="1">
         <v>966.21</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="1">
+        <v>618.97</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1566.82</v>
+      </c>
+      <c r="I2" s="1">
+        <v>544.38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
-        <v>727.88</v>
+        <v>727.8800000000001</v>
       </c>
       <c r="D3" s="1">
         <v>590.97</v>
@@ -1271,10 +1298,19 @@
       <c r="F3" s="1">
         <v>846.47</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="1">
+        <v>422.0599999999999</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1381.64</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1584.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>1020.85</v>
@@ -1286,12 +1322,21 @@
         <v>976.84</v>
       </c>
       <c r="F4" s="1">
-        <v>745.4699999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>745.47</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1435.52</v>
+      </c>
+      <c r="H4" s="1">
+        <v>853.51</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1398.51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>198.98</v>
@@ -1305,16 +1350,25 @@
       <c r="F5" s="1">
         <v>1012.83</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="1">
+        <v>1236.83</v>
+      </c>
+      <c r="H5" s="1">
+        <v>184.95</v>
+      </c>
+      <c r="I5" s="1">
+        <v>999.26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>481.76</v>
       </c>
       <c r="D6" s="1">
-        <v>936.72</v>
+        <v>936.7199999999999</v>
       </c>
       <c r="E6" s="1">
         <v>378.7</v>
@@ -1322,10 +1376,19 @@
       <c r="F6" s="1">
         <v>430.53</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="1">
+        <v>809.38</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1061.61</v>
+      </c>
+      <c r="I6" s="1">
+        <v>338.24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1">
         <v>454.03</v>
@@ -1339,13 +1402,22 @@
       <c r="F7" s="1">
         <v>1242.23</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="1">
+        <v>898.45</v>
+      </c>
+      <c r="H7" s="1">
+        <v>802.4000000000001</v>
+      </c>
+      <c r="I7" s="1">
+        <v>239.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
-        <v>305.4599999999999</v>
+        <v>305.46</v>
       </c>
       <c r="D8" s="1">
         <v>391.93</v>
@@ -1356,16 +1428,25 @@
       <c r="F8" s="1">
         <v>1065.46</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="1">
+        <v>74.7</v>
+      </c>
+      <c r="H8" s="1">
+        <v>382.95</v>
+      </c>
+      <c r="I8" s="1">
+        <v>138.55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1">
         <v>529.97</v>
       </c>
       <c r="D9" s="1">
-        <v>440.13</v>
+        <v>440.1300000000001</v>
       </c>
       <c r="E9" s="1">
         <v>99.99000000000001</v>
@@ -1373,10 +1454,19 @@
       <c r="F9" s="1">
         <v>358.78</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="1">
+        <v>28.45</v>
+      </c>
+      <c r="H9" s="1">
+        <v>685</v>
+      </c>
+      <c r="I9" s="1">
+        <v>598.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1">
         <v>134.49</v>
@@ -1390,16 +1480,25 @@
       <c r="F10" s="1">
         <v>29.99</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="1">
+        <v>109.98</v>
+      </c>
+      <c r="H10" s="1">
+        <v>225.91</v>
+      </c>
+      <c r="I10" s="1">
+        <v>219.98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1">
         <v>764</v>
       </c>
       <c r="D11" s="1">
-        <v>447.42</v>
+        <v>447.4200000000001</v>
       </c>
       <c r="E11" s="1">
         <v>1048.35</v>
@@ -1407,10 +1506,19 @@
       <c r="F11" s="1">
         <v>677.9299999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="1">
+        <v>1917.7</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1578</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1678.65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1">
         <v>189.18</v>
@@ -1424,10 +1532,19 @@
       <c r="F12" s="1">
         <v>456.71</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="1">
+        <v>234.47</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1059.82</v>
+      </c>
+      <c r="I12" s="1">
+        <v>341.97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1">
         <v>148.2</v>
@@ -1441,16 +1558,25 @@
       <c r="F13" s="1">
         <v>625.9</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" s="1">
+        <v>547.33</v>
+      </c>
+      <c r="H13" s="1">
+        <v>330.3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>844.8000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1">
         <v>1060.53</v>
       </c>
       <c r="D14" s="1">
-        <v>886.0400000000001</v>
+        <v>886.04</v>
       </c>
       <c r="E14" s="1">
         <v>281.95</v>
@@ -1458,10 +1584,19 @@
       <c r="F14" s="1">
         <v>1295.93</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="1">
+        <v>293.14</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1275.63</v>
+      </c>
+      <c r="I14" s="1">
+        <v>287.46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
         <v>1546.44</v>
@@ -1475,10 +1610,19 @@
       <c r="F15" s="1">
         <v>1244.17</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" s="1">
+        <v>1210.94</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2069.23</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1057.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1">
         <v>219.97</v>
@@ -1492,10 +1636,19 @@
       <c r="F16" s="1">
         <v>207.96</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="1">
+        <v>169.96</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1087.35</v>
+      </c>
+      <c r="I16" s="1">
+        <v>272.46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1">
         <v>135.47</v>
@@ -1509,10 +1662,19 @@
       <c r="F17" s="1">
         <v>1440.79</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="1">
+        <v>581.45</v>
+      </c>
+      <c r="H17" s="1">
+        <v>908.8800000000001</v>
+      </c>
+      <c r="I17" s="1">
+        <v>372.89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C18" s="1">
         <v>90.00999999999999</v>
@@ -1526,10 +1688,19 @@
       <c r="F18" s="1">
         <v>67.98</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="1">
+        <v>49.99</v>
+      </c>
+      <c r="H18" s="1">
+        <v>505.17</v>
+      </c>
+      <c r="I18" s="1">
+        <v>52.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C19" s="1">
         <v>904.6799999999999</v>
@@ -1543,16 +1714,25 @@
       <c r="F19" s="1">
         <v>864.2900000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="1">
+        <v>185.2</v>
+      </c>
+      <c r="H19" s="1">
+        <v>757.36</v>
+      </c>
+      <c r="I19" s="1">
+        <v>876.97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1">
         <v>494.43</v>
       </c>
       <c r="D20" s="1">
-        <v>374.64</v>
+        <v>374.6400000000001</v>
       </c>
       <c r="E20" s="1">
         <v>502.47</v>
@@ -1560,16 +1740,25 @@
       <c r="F20" s="1">
         <v>288.45</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="1">
+        <v>404.53</v>
+      </c>
+      <c r="H20" s="1">
+        <v>552.61</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1233.91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1">
         <v>197.87</v>
       </c>
       <c r="D21" s="1">
-        <v>76.23999999999999</v>
+        <v>76.24000000000001</v>
       </c>
       <c r="E21" s="1">
         <v>149.14</v>
@@ -1577,10 +1766,19 @@
       <c r="F21" s="1">
         <v>41.98</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="1">
+        <v>404.86</v>
+      </c>
+      <c r="H21" s="1">
+        <v>354.59</v>
+      </c>
+      <c r="I21" s="1">
+        <v>779.11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1">
         <v>28.38</v>
@@ -1594,10 +1792,19 @@
       <c r="F22" s="1">
         <v>278.48</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="1">
+        <v>269.94</v>
+      </c>
+      <c r="H22" s="1">
+        <v>74.98</v>
+      </c>
+      <c r="I22" s="1">
+        <v>756.74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1">
         <v>223.95</v>
@@ -1611,10 +1818,19 @@
       <c r="F23" s="1">
         <v>582.08</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="1">
+        <v>178.47</v>
+      </c>
+      <c r="H23" s="1">
+        <v>121.5</v>
+      </c>
+      <c r="I23" s="1">
+        <v>286.44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C24" s="1">
         <v>388.9200000000001</v>
@@ -1628,16 +1844,25 @@
       <c r="F24" s="1">
         <v>455.89</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="1">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="H24" s="1">
+        <v>104.48</v>
+      </c>
+      <c r="I24" s="1">
+        <v>537.47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C25" s="1">
         <v>59.29</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E25" s="1">
         <v>45.68</v>
@@ -1645,10 +1870,19 @@
       <c r="F25" s="1">
         <v>434.46</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="1">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="H25" s="1">
+        <v>213.94</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C26" s="1">
         <v>1201.85</v>
@@ -1662,16 +1896,25 @@
       <c r="F26" s="1">
         <v>1001.4</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="1">
+        <v>1053.25</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1854.51</v>
+      </c>
+      <c r="I26" s="1">
+        <v>980.6600000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C27" s="1">
         <v>130.45</v>
       </c>
       <c r="D27" s="1">
-        <v>450.8800000000001</v>
+        <v>450.88</v>
       </c>
       <c r="E27" s="1">
         <v>119.97</v>
@@ -1679,27 +1922,45 @@
       <c r="F27" s="1">
         <v>332.96</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="1">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="H27" s="1">
+        <v>537.89</v>
+      </c>
+      <c r="I27" s="1">
+        <v>245.45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1">
         <v>502.96</v>
       </c>
       <c r="D28" s="1">
-        <v>728.39</v>
+        <v>728.3900000000001</v>
       </c>
       <c r="E28" s="1">
-        <v>923.89</v>
+        <v>923.8899999999999</v>
       </c>
       <c r="F28" s="1">
         <v>889.14</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="1">
+        <v>276.7</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1696.27</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1209.84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C29" s="1">
         <v>1362.99</v>
@@ -1713,27 +1974,45 @@
       <c r="F29" s="1">
         <v>844.47</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" s="1">
+        <v>1730.59</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2735.649999999999</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1750.99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1">
         <v>226.95</v>
       </c>
       <c r="D30" s="1">
-        <v>423.4800000000001</v>
+        <v>423.48</v>
       </c>
       <c r="E30" s="1">
         <v>58.09</v>
       </c>
       <c r="F30" s="1">
-        <v>513.66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>513.6600000000001</v>
+      </c>
+      <c r="G30" s="1">
+        <v>921.1700000000001</v>
+      </c>
+      <c r="H30" s="1">
+        <v>706.45</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1318.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C31" s="1">
         <v>189.98</v>
@@ -1747,10 +2026,19 @@
       <c r="F31" s="1">
         <v>195.46</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" s="1">
+        <v>687.49</v>
+      </c>
+      <c r="H31" s="1">
+        <v>323.89</v>
+      </c>
+      <c r="I31" s="1">
+        <v>546.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C32" s="1">
         <v>756.8200000000001</v>
@@ -1764,10 +2052,19 @@
       <c r="F32" s="1">
         <v>240.97</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32" s="1">
+        <v>1167.93</v>
+      </c>
+      <c r="H32" s="1">
+        <v>4470.079999999998</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1610.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C33" s="1">
         <v>1735.14</v>
@@ -1779,12 +2076,21 @@
         <v>1973.05</v>
       </c>
       <c r="F33" s="1">
-        <v>551.8800000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>551.88</v>
+      </c>
+      <c r="G33" s="1">
+        <v>962.1799999999999</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2361.79</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2126.33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C34" s="1">
         <v>1341.33</v>
@@ -1793,15 +2099,24 @@
         <v>5281.63</v>
       </c>
       <c r="E34" s="1">
-        <v>3712.320000000001</v>
+        <v>3712.319999999999</v>
       </c>
       <c r="F34" s="1">
         <v>3936.82</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" s="1">
+        <v>4285.439999999999</v>
+      </c>
+      <c r="H34" s="1">
+        <v>5441.95</v>
+      </c>
+      <c r="I34" s="1">
+        <v>5348.169999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C35" s="1">
         <v>318.45</v>
@@ -1815,16 +2130,25 @@
       <c r="F35" s="1">
         <v>172.08</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="1">
+        <v>340.23</v>
+      </c>
+      <c r="H35" s="1">
+        <v>834.5999999999999</v>
+      </c>
+      <c r="I35" s="1">
+        <v>175.95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C36" s="1">
         <v>830.1100000000001</v>
       </c>
       <c r="D36" s="1">
-        <v>454.6999999999999</v>
+        <v>454.7</v>
       </c>
       <c r="E36" s="1">
         <v>1203.38</v>
@@ -1832,13 +2156,22 @@
       <c r="F36" s="1">
         <v>294.55</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="1">
+        <v>1774.63</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1911.21</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1327.51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C37" s="1">
-        <v>2152.86</v>
+        <v>2152.860000000001</v>
       </c>
       <c r="D37" s="1">
         <v>2468.03</v>
@@ -1849,10 +2182,19 @@
       <c r="F37" s="1">
         <v>1375.04</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" s="1">
+        <v>3055.82</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2103.65</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1797.16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C38" s="1">
         <v>154.97</v>
@@ -1864,12 +2206,21 @@
         <v>57.48</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G38" s="1">
+        <v>59.99</v>
+      </c>
+      <c r="H38" s="1">
+        <v>487.97</v>
+      </c>
+      <c r="I38" s="1">
+        <v>174.96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C39" s="1">
         <v>178.78</v>
@@ -1883,16 +2234,25 @@
       <c r="F39" s="1">
         <v>213.46</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" s="1">
+        <v>109.46</v>
+      </c>
+      <c r="H39" s="1">
+        <v>830.49</v>
+      </c>
+      <c r="I39" s="1">
+        <v>484.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C40" s="1">
         <v>368.55</v>
       </c>
       <c r="D40" s="1">
-        <v>789.8399999999999</v>
+        <v>789.84</v>
       </c>
       <c r="E40" s="1">
         <v>641.27</v>
@@ -1900,10 +2260,19 @@
       <c r="F40" s="1">
         <v>362.46</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" s="1">
+        <v>354.14</v>
+      </c>
+      <c r="H40" s="1">
+        <v>740.7900000000001</v>
+      </c>
+      <c r="I40" s="1">
+        <v>516.3100000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C41" s="1">
         <v>457.14</v>
@@ -1917,27 +2286,45 @@
       <c r="F41" s="1">
         <v>173.97</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="G41" s="1">
+        <v>504.0599999999999</v>
+      </c>
+      <c r="H41" s="1">
+        <v>713.46</v>
+      </c>
+      <c r="I41" s="1">
+        <v>825.3500000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C42" s="1">
         <v>1359.48</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E42" s="1">
         <v>382.99</v>
       </c>
       <c r="F42" s="1">
-        <v>551.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>551.8000000000001</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1007.1</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2223.48</v>
+      </c>
+      <c r="I42" s="1">
+        <v>626.97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C43" s="1">
         <v>44.48</v>
@@ -1951,10 +2338,19 @@
       <c r="F43" s="1">
         <v>125.96</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" s="1">
+        <v>291.44</v>
+      </c>
+      <c r="H43" s="1">
+        <v>61.94</v>
+      </c>
+      <c r="I43" s="1">
+        <v>424.66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C44" s="1">
         <v>363.79</v>
@@ -1968,27 +2364,45 @@
       <c r="F44" s="1">
         <v>724.0599999999999</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" s="1">
+        <v>838.3200000000002</v>
+      </c>
+      <c r="H44" s="1">
+        <v>582.33</v>
+      </c>
+      <c r="I44" s="1">
+        <v>311.66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C45" s="1">
         <v>1070.34</v>
       </c>
       <c r="D45" s="1">
-        <v>692.49</v>
+        <v>692.4900000000001</v>
       </c>
       <c r="E45" s="1">
-        <v>476.9100000000001</v>
+        <v>476.91</v>
       </c>
       <c r="F45" s="1">
-        <v>469.95</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>469.9499999999999</v>
+      </c>
+      <c r="G45" s="1">
+        <v>580.25</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1987.78</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1235.66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C46" s="1">
         <v>135.98</v>
@@ -2002,10 +2416,19 @@
       <c r="F46" s="1">
         <v>695.14</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="G46" s="1">
+        <v>1116.18</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1637.91</v>
+      </c>
+      <c r="I46" s="1">
+        <v>2206.29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C47" s="1">
         <v>475.3700000000001</v>
@@ -2014,15 +2437,24 @@
         <v>667.73</v>
       </c>
       <c r="E47" s="1">
-        <v>296.43</v>
+        <v>296.4300000000001</v>
       </c>
       <c r="F47" s="1">
-        <v>382.9300000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>382.93</v>
+      </c>
+      <c r="G47" s="1">
+        <v>233.53</v>
+      </c>
+      <c r="H47" s="1">
+        <v>657.24</v>
+      </c>
+      <c r="I47" s="1">
+        <v>993.6700000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C48" s="1">
         <v>911.3099999999999</v>
@@ -2036,13 +2468,22 @@
       <c r="F48" s="1">
         <v>754.4200000000001</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" s="1">
+        <v>665.0900000000001</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2078.76</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1666.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C49" s="1">
-        <v>875.35</v>
+        <v>875.3499999999999</v>
       </c>
       <c r="D49" s="1">
         <v>672.45</v>
@@ -2053,10 +2494,19 @@
       <c r="F49" s="1">
         <v>925.6500000000001</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="G49" s="1">
+        <v>1196.73</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1846.95</v>
+      </c>
+      <c r="I49" s="1">
+        <v>3640.849999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C50" s="1">
         <v>241.37</v>
@@ -2068,12 +2518,21 @@
         <v>79.98</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G50" s="1">
+        <v>159.97</v>
+      </c>
+      <c r="H50" s="1">
+        <v>433.95</v>
+      </c>
+      <c r="I50" s="1">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C51" s="1">
         <v>549.71</v>
@@ -2087,10 +2546,19 @@
       <c r="F51" s="1">
         <v>314.98</v>
       </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="G51" s="1">
+        <v>574.49</v>
+      </c>
+      <c r="H51" s="1">
+        <v>686.8900000000001</v>
+      </c>
+      <c r="I51" s="1">
+        <v>112.97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C52" s="1">
         <v>209.05</v>
@@ -2104,10 +2572,19 @@
       <c r="F52" s="1">
         <v>225.6</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="G52" s="1">
+        <v>48.09999999999999</v>
+      </c>
+      <c r="H52" s="1">
+        <v>290.86</v>
+      </c>
+      <c r="I52" s="1">
+        <v>450.99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C53" s="1">
         <v>1106.41</v>
@@ -2121,10 +2598,19 @@
       <c r="F53" s="1">
         <v>211.99</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" s="1">
+        <v>590.36</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1181.75</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1561.07</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C54" s="1">
         <v>176.26</v>
@@ -2138,10 +2624,19 @@
       <c r="F54" s="1">
         <v>121.96</v>
       </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54" s="1">
+        <v>135.98</v>
+      </c>
+      <c r="H54" s="1">
+        <v>149.19</v>
+      </c>
+      <c r="I54" s="1">
+        <v>85.97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C55" s="1">
         <v>430.4300000000001</v>
@@ -2155,10 +2650,19 @@
       <c r="F55" s="1">
         <v>400.95</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" s="1">
+        <v>531.36</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1158.26</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1110.21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C56" s="1">
         <v>473.0700000000001</v>
@@ -2172,33 +2676,51 @@
       <c r="F56" s="1">
         <v>165.95</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" s="1">
+        <v>425.4400000000001</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1335.35</v>
+      </c>
+      <c r="I56" s="1">
+        <v>536.27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C57" s="1">
-        <v>27227.63</v>
+        <v>27227.63000000001</v>
       </c>
       <c r="D57" s="1">
         <v>26739.29</v>
       </c>
       <c r="E57" s="1">
-        <v>35470.47</v>
+        <v>35470.46999999999</v>
       </c>
       <c r="F57" s="1">
         <v>15090.82</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57" s="1">
+        <v>13361.95</v>
+      </c>
+      <c r="H57" s="1">
+        <v>19963.59</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C58" s="1">
-        <v>971.9</v>
+        <v>971.9000000000001</v>
       </c>
       <c r="D58" s="1">
-        <v>573.8200000000001</v>
+        <v>573.8199999999999</v>
       </c>
       <c r="E58" s="1">
         <v>102.98</v>
@@ -2206,10 +2728,19 @@
       <c r="F58" s="1">
         <v>90.83</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" s="1">
+        <v>54.96999999999998</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1699.41</v>
+      </c>
+      <c r="I58" s="1">
+        <v>726.64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C59" s="1">
         <v>472.66</v>
@@ -2223,27 +2754,45 @@
       <c r="F59" s="1">
         <v>293.2</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" s="1">
+        <v>460.47</v>
+      </c>
+      <c r="H59" s="1">
+        <v>424.39</v>
+      </c>
+      <c r="I59" s="1">
+        <v>733.1099999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C60" s="1">
         <v>47.99</v>
       </c>
       <c r="D60" s="1">
-        <v>22.64</v>
+        <v>22.63999999999999</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F60" s="1">
         <v>68.48</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" s="1">
+        <v>250.24</v>
+      </c>
+      <c r="H60" s="1">
+        <v>534.1300000000001</v>
+      </c>
+      <c r="I60" s="1">
+        <v>341.07</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C61" s="1">
         <v>1845.8</v>
@@ -2257,10 +2806,19 @@
       <c r="F61" s="1">
         <v>1766.65</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61" s="1">
+        <v>1844.21</v>
+      </c>
+      <c r="H61" s="1">
+        <v>1807.36</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1348.74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C62" s="1">
         <v>19.99</v>
@@ -2269,15 +2827,24 @@
         <v>238.35</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F62" s="1">
         <v>128.98</v>
       </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="G62" s="1">
+        <v>23.46</v>
+      </c>
+      <c r="H62" s="1">
+        <v>546.0699999999999</v>
+      </c>
+      <c r="I62" s="1">
+        <v>16.29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C63" s="1">
         <v>1881.58</v>
@@ -2286,21 +2853,30 @@
         <v>1386.79</v>
       </c>
       <c r="E63" s="1">
-        <v>735.55</v>
+        <v>735.5500000000002</v>
       </c>
       <c r="F63" s="1">
         <v>571.08</v>
       </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63" s="1">
+        <v>582.96</v>
+      </c>
+      <c r="H63" s="1">
+        <v>1582.13</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1264.38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C64" s="1">
         <v>403.43</v>
       </c>
       <c r="D64" s="1">
-        <v>662.87</v>
+        <v>662.8700000000001</v>
       </c>
       <c r="E64" s="1">
         <v>672.3900000000001</v>
@@ -2308,10 +2884,19 @@
       <c r="F64" s="1">
         <v>790.72</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="G64" s="1">
+        <v>99.97999999999999</v>
+      </c>
+      <c r="H64" s="1">
+        <v>824.53</v>
+      </c>
+      <c r="I64" s="1">
+        <v>634.8100000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C65" s="1">
         <v>219.11</v>
@@ -2325,10 +2910,19 @@
       <c r="F65" s="1">
         <v>44.99</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65" s="1">
+        <v>96.47</v>
+      </c>
+      <c r="H65" s="1">
+        <v>454.4200000000001</v>
+      </c>
+      <c r="I65" s="1">
+        <v>94.98999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C66" s="1">
         <v>115.47</v>
@@ -2337,21 +2931,30 @@
         <v>387.96</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F66" s="1">
         <v>187.58</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66" s="1">
+        <v>236.27</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1014.47</v>
+      </c>
+      <c r="I66" s="1">
+        <v>590.53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C67" s="1">
         <v>29.99</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E67" s="1">
         <v>297.84</v>
@@ -2359,10 +2962,19 @@
       <c r="F67" s="1">
         <v>120.96</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67" s="1">
+        <v>160.95</v>
+      </c>
+      <c r="H67" s="1">
+        <v>222.73</v>
+      </c>
+      <c r="I67" s="1">
+        <v>263.36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C68" s="1">
         <v>652.4000000000001</v>
@@ -2376,10 +2988,19 @@
       <c r="F68" s="1">
         <v>-80.80000000000001</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="G68" s="1">
+        <v>49.98</v>
+      </c>
+      <c r="H68" s="1">
+        <v>729.61</v>
+      </c>
+      <c r="I68" s="1">
+        <v>505.1900000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C69" s="1">
         <v>107.79</v>
@@ -2391,12 +3012,21 @@
         <v>375.95</v>
       </c>
       <c r="F69" s="1">
-        <v>134.8999999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>134.9</v>
+      </c>
+      <c r="G69" s="1">
+        <v>590.4</v>
+      </c>
+      <c r="H69" s="1">
+        <v>257.94</v>
+      </c>
+      <c r="I69" s="1">
+        <v>458.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C70" s="1">
         <v>386.43</v>
@@ -2410,27 +3040,45 @@
       <c r="F70" s="1">
         <v>517.73</v>
       </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="G70" s="1">
+        <v>1201.79</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1988.26</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1162.03</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E71" s="1">
         <v>383.98</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G71" s="1">
+        <v>193.07</v>
+      </c>
+      <c r="H71" s="1">
+        <v>202.1</v>
+      </c>
+      <c r="I71" s="1">
+        <v>465.47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C72" s="1">
         <v>299.27</v>
@@ -2444,10 +3092,19 @@
       <c r="F72" s="1">
         <v>335.91</v>
       </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72" s="1">
+        <v>24.49</v>
+      </c>
+      <c r="H72" s="1">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="I72" s="1">
+        <v>345.46</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C73" s="1">
         <v>331.95</v>
@@ -2461,10 +3118,19 @@
       <c r="F73" s="1">
         <v>245.14</v>
       </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="G73" s="1">
+        <v>1106.87</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1317.87</v>
+      </c>
+      <c r="I73" s="1">
+        <v>697.01</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C74" s="1">
         <v>326.93</v>
@@ -2478,10 +3144,19 @@
       <c r="F74" s="1">
         <v>186.57</v>
       </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="G74" s="1">
+        <v>168.19</v>
+      </c>
+      <c r="H74" s="1">
+        <v>692.2800000000001</v>
+      </c>
+      <c r="I74" s="1">
+        <v>383.4300000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C75" s="1">
         <v>203.99</v>
@@ -2495,10 +3170,19 @@
       <c r="F75" s="1">
         <v>162.09</v>
       </c>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="G75" s="1">
+        <v>501.46</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1091.06</v>
+      </c>
+      <c r="I75" s="1">
+        <v>677.6500000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C76" s="1">
         <v>738.38</v>
@@ -2512,10 +3196,19 @@
       <c r="F76" s="1">
         <v>834.58</v>
       </c>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="G76" s="1">
+        <v>893.51</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1249.41</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1484.93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C77" s="1">
         <v>358.12</v>
@@ -2529,10 +3222,19 @@
       <c r="F77" s="1">
         <v>201.99</v>
       </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="G77" s="1">
+        <v>209.97</v>
+      </c>
+      <c r="H77" s="1">
+        <v>891.37</v>
+      </c>
+      <c r="I77" s="1">
+        <v>1541.01</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C78" s="1">
         <v>171.97</v>
@@ -2546,16 +3248,25 @@
       <c r="F78" s="1">
         <v>-83.97999999999999</v>
       </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="G78" s="1">
+        <v>134.98</v>
+      </c>
+      <c r="H78" s="1">
+        <v>149.48</v>
+      </c>
+      <c r="I78" s="1">
+        <v>550.27</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C79" s="1">
         <v>196.47</v>
       </c>
       <c r="D79" s="1">
-        <v>902.8399999999999</v>
+        <v>902.8400000000001</v>
       </c>
       <c r="E79" s="1">
         <v>230.97</v>
@@ -2563,10 +3274,19 @@
       <c r="F79" s="1">
         <v>770.97</v>
       </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="G79" s="1">
+        <v>482.38</v>
+      </c>
+      <c r="H79" s="1">
+        <v>1142.28</v>
+      </c>
+      <c r="I79" s="1">
+        <v>748.24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C80" s="1">
         <v>268.23</v>
@@ -2575,15 +3295,24 @@
         <v>516.97</v>
       </c>
       <c r="E80" s="1">
-        <v>418.0999999999999</v>
+        <v>418.1</v>
       </c>
       <c r="F80" s="1">
-        <v>382.6500000000001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>382.65</v>
+      </c>
+      <c r="G80" s="1">
+        <v>905.2900000000001</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1397.8</v>
+      </c>
+      <c r="I80" s="1">
+        <v>1574.07</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C81" s="1">
         <v>270.93</v>
@@ -2595,18 +3324,27 @@
         <v>485.47</v>
       </c>
       <c r="F81" s="1">
-        <v>424.88</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+        <v>424.8800000000001</v>
+      </c>
+      <c r="G81" s="1">
+        <v>491.86</v>
+      </c>
+      <c r="H81" s="1">
+        <v>1196.53</v>
+      </c>
+      <c r="I81" s="1">
+        <v>599.83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C82" s="1">
         <v>1115.65</v>
       </c>
       <c r="D82" s="1">
-        <v>-172.8699999999999</v>
+        <v>-172.87</v>
       </c>
       <c r="E82" s="1">
         <v>206.97</v>
@@ -2614,10 +3352,19 @@
       <c r="F82" s="1">
         <v>248.46</v>
       </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="G82" s="1">
+        <v>130.91</v>
+      </c>
+      <c r="H82" s="1">
+        <v>1154.88</v>
+      </c>
+      <c r="I82" s="1">
+        <v>418.26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C83" s="1">
         <v>113.98</v>
@@ -2631,10 +3378,19 @@
       <c r="F83" s="1">
         <v>197.85</v>
       </c>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="G83" s="1">
+        <v>185.97</v>
+      </c>
+      <c r="H83" s="1">
+        <v>651.4200000000001</v>
+      </c>
+      <c r="I83" s="1">
+        <v>1338.68</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C84" s="1">
         <v>209.95</v>
@@ -2648,10 +3404,19 @@
       <c r="F84" s="1">
         <v>169.98</v>
       </c>
-    </row>
-    <row r="85" spans="1:6">
+      <c r="G84" s="1">
+        <v>55.79</v>
+      </c>
+      <c r="H84" s="1">
+        <v>446.8199999999999</v>
+      </c>
+      <c r="I84" s="1">
+        <v>366.97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C85" s="1">
         <v>1347.14</v>
@@ -2665,10 +3430,19 @@
       <c r="F85" s="1">
         <v>2134.78</v>
       </c>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="G85" s="1">
+        <v>1409.59</v>
+      </c>
+      <c r="H85" s="1">
+        <v>2510.639999999999</v>
+      </c>
+      <c r="I85" s="1">
+        <v>3056.52</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C86" s="1">
         <v>596.0700000000001</v>
@@ -2682,10 +3456,19 @@
       <c r="F86" s="1">
         <v>564.9400000000001</v>
       </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="G86" s="1">
+        <v>466.1799999999999</v>
+      </c>
+      <c r="H86" s="1">
+        <v>345.55</v>
+      </c>
+      <c r="I86" s="1">
+        <v>870.4000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C87" s="1">
         <v>96.47</v>
@@ -2694,15 +3477,24 @@
         <v>446.27</v>
       </c>
       <c r="E87" s="1">
-        <v>472.94</v>
+        <v>472.9400000000001</v>
       </c>
       <c r="F87" s="1">
         <v>170.64</v>
       </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="G87" s="1">
+        <v>110.96</v>
+      </c>
+      <c r="H87" s="1">
+        <v>1537.72</v>
+      </c>
+      <c r="I87" s="1">
+        <v>1267.01</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C88" s="1">
         <v>211.27</v>
@@ -2716,10 +3508,19 @@
       <c r="F88" s="1">
         <v>595.66</v>
       </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="G88" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="H88" s="1">
+        <v>514.9300000000001</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C89" s="1">
         <v>16.29</v>
@@ -2733,27 +3534,45 @@
       <c r="F89" s="1">
         <v>64.98999999999999</v>
       </c>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="G89" s="1">
+        <v>139.45</v>
+      </c>
+      <c r="H89" s="1">
+        <v>556.36</v>
+      </c>
+      <c r="I89" s="1">
+        <v>688.76</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C90" s="1">
         <v>499.95</v>
       </c>
       <c r="D90" s="1">
-        <v>71.94999999999996</v>
+        <v>71.95000000000002</v>
       </c>
       <c r="E90" s="1">
         <v>470.64</v>
       </c>
       <c r="F90" s="1">
-        <v>289.93</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+        <v>289.9299999999999</v>
+      </c>
+      <c r="G90" s="1">
+        <v>784.6199999999999</v>
+      </c>
+      <c r="H90" s="1">
+        <v>1361.98</v>
+      </c>
+      <c r="I90" s="1">
+        <v>1248.64</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C91" s="1">
         <v>210.96</v>
@@ -2762,15 +3581,24 @@
         <v>55.7</v>
       </c>
       <c r="E91" s="1">
-        <v>282.18</v>
+        <v>282.1799999999999</v>
       </c>
       <c r="F91" s="1">
         <v>371.96</v>
       </c>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="G91" s="1">
+        <v>737.36</v>
+      </c>
+      <c r="H91" s="1">
+        <v>833.71</v>
+      </c>
+      <c r="I91" s="1">
+        <v>150.96</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C92" s="1">
         <v>557.85</v>
@@ -2784,13 +3612,22 @@
       <c r="F92" s="1">
         <v>1246.76</v>
       </c>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="G92" s="1">
+        <v>866.02</v>
+      </c>
+      <c r="H92" s="1">
+        <v>2456.45</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1215.93</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C93" s="1">
-        <v>373.8699999999999</v>
+        <v>373.87</v>
       </c>
       <c r="D93" s="1">
         <v>69.19</v>
@@ -2801,27 +3638,45 @@
       <c r="F93" s="1">
         <v>123.83</v>
       </c>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="G93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H93" s="1">
+        <v>368</v>
+      </c>
+      <c r="I93" s="1">
+        <v>111.97</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C94" s="1">
-        <v>2504.51</v>
+        <v>2504.509999999999</v>
       </c>
       <c r="D94" s="1">
         <v>1038.08</v>
       </c>
       <c r="E94" s="1">
-        <v>518.3099999999999</v>
+        <v>518.3100000000001</v>
       </c>
       <c r="F94" s="1">
         <v>2248.04</v>
       </c>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="G94" s="1">
+        <v>816.04</v>
+      </c>
+      <c r="H94" s="1">
+        <v>1577.29</v>
+      </c>
+      <c r="I94" s="1">
+        <v>1256.19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C95" s="1">
         <v>449.43</v>
@@ -2835,10 +3690,19 @@
       <c r="F95" s="1">
         <v>1069.91</v>
       </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="G95" s="1">
+        <v>903.6799999999999</v>
+      </c>
+      <c r="H95" s="1">
+        <v>1368.84</v>
+      </c>
+      <c r="I95" s="1">
+        <v>818.6799999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C96" s="1">
         <v>728.3</v>
@@ -2852,10 +3716,19 @@
       <c r="F96" s="1">
         <v>1804.02</v>
       </c>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="G96" s="1">
+        <v>591.73</v>
+      </c>
+      <c r="H96" s="1">
+        <v>1024.13</v>
+      </c>
+      <c r="I96" s="1">
+        <v>1937.9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C97" s="1">
         <v>387.99</v>
@@ -2864,15 +3737,24 @@
         <v>421.46</v>
       </c>
       <c r="E97" s="1">
-        <v>393.44</v>
+        <v>393.4400000000001</v>
       </c>
       <c r="F97" s="1">
         <v>461.3200000000001</v>
       </c>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="G97" s="1">
+        <v>291.45</v>
+      </c>
+      <c r="H97" s="1">
+        <v>818.7900000000001</v>
+      </c>
+      <c r="I97" s="1">
+        <v>1297.78</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C98" s="1">
         <v>122.99</v>
@@ -2886,10 +3768,19 @@
       <c r="F98" s="1">
         <v>20.49</v>
       </c>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="G98" s="1">
+        <v>212.66</v>
+      </c>
+      <c r="H98" s="1">
+        <v>837.9000000000001</v>
+      </c>
+      <c r="I98" s="1">
+        <v>629.91</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C99" s="1">
         <v>532.9400000000001</v>
@@ -2903,16 +3794,25 @@
       <c r="F99" s="1">
         <v>17.99</v>
       </c>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="G99" s="1">
+        <v>104.65</v>
+      </c>
+      <c r="H99" s="1">
+        <v>203.34</v>
+      </c>
+      <c r="I99" s="1">
+        <v>476.39</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C100" s="1">
         <v>350.18</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E100" s="1">
         <v>185.73</v>
@@ -2920,10 +3820,19 @@
       <c r="F100" s="1">
         <v>349.5</v>
       </c>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="G100" s="1">
+        <v>408.93</v>
+      </c>
+      <c r="H100" s="1">
+        <v>798.8900000000001</v>
+      </c>
+      <c r="I100" s="1">
+        <v>275.95</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C101" s="1">
         <v>481.09</v>
@@ -2937,10 +3846,19 @@
       <c r="F101" s="1">
         <v>89.25</v>
       </c>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="G101" s="1">
+        <v>575.54</v>
+      </c>
+      <c r="H101" s="1">
+        <v>712.8200000000002</v>
+      </c>
+      <c r="I101" s="1">
+        <v>1150.78</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C102" s="1">
         <v>670.4100000000001</v>
@@ -2954,27 +3872,45 @@
       <c r="F102" s="1">
         <v>684.75</v>
       </c>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="G102" s="1">
+        <v>618.12</v>
+      </c>
+      <c r="H102" s="1">
+        <v>319.9000000000001</v>
+      </c>
+      <c r="I102" s="1">
+        <v>1041.64</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C103" s="1">
         <v>222.73</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E103" s="1">
         <v>133.99</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G103" s="1">
+        <v>137.75</v>
+      </c>
+      <c r="H103" s="1">
+        <v>348.49</v>
+      </c>
+      <c r="I103" s="1">
+        <v>603.0400000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C104" s="1">
         <v>222.95</v>
@@ -2988,10 +3924,19 @@
       <c r="F104" s="1">
         <v>308.43</v>
       </c>
-    </row>
-    <row r="105" spans="1:6">
+      <c r="G104" s="1">
+        <v>208.89</v>
+      </c>
+      <c r="H104" s="1">
+        <v>321.96</v>
+      </c>
+      <c r="I104" s="1">
+        <v>187.95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C105" s="1">
         <v>743.0700000000001</v>
@@ -3003,12 +3948,21 @@
         <v>77.47</v>
       </c>
       <c r="F105" s="1">
-        <v>429.9200000000001</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+        <v>429.92</v>
+      </c>
+      <c r="G105" s="1">
+        <v>404.97</v>
+      </c>
+      <c r="H105" s="1">
+        <v>547.3200000000001</v>
+      </c>
+      <c r="I105" s="1">
+        <v>1114.12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C106" s="1">
         <v>250.82</v>
@@ -3022,10 +3976,19 @@
       <c r="F106" s="1">
         <v>117.07</v>
       </c>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="G106" s="1">
+        <v>228.98</v>
+      </c>
+      <c r="H106" s="1">
+        <v>701.0300000000001</v>
+      </c>
+      <c r="I106" s="1">
+        <v>150.18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C107" s="1">
         <v>416.39</v>
@@ -3039,10 +4002,19 @@
       <c r="F107" s="1">
         <v>236.96</v>
       </c>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="G107" s="1">
+        <v>364.96</v>
+      </c>
+      <c r="H107" s="1">
+        <v>900.86</v>
+      </c>
+      <c r="I107" s="1">
+        <v>311.26</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C108" s="1">
         <v>1165.41</v>
@@ -3056,13 +4028,22 @@
       <c r="F108" s="1">
         <v>17.99</v>
       </c>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="G108" s="1">
+        <v>593.46</v>
+      </c>
+      <c r="H108" s="1">
+        <v>597.6799999999999</v>
+      </c>
+      <c r="I108" s="1">
+        <v>479.89</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C109" s="1">
-        <v>707.0799999999999</v>
+        <v>707.08</v>
       </c>
       <c r="D109" s="1">
         <v>152.96</v>
@@ -3073,10 +4054,19 @@
       <c r="F109" s="1">
         <v>1012.37</v>
       </c>
-    </row>
-    <row r="110" spans="1:6">
+      <c r="G109" s="1">
+        <v>425.5500000000001</v>
+      </c>
+      <c r="H109" s="1">
+        <v>576.3200000000001</v>
+      </c>
+      <c r="I109" s="1">
+        <v>301.05</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C110" s="1">
         <v>258.41</v>
@@ -3090,10 +4080,19 @@
       <c r="F110" s="1">
         <v>497.53</v>
       </c>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="G110" s="1">
+        <v>263.46</v>
+      </c>
+      <c r="H110" s="1">
+        <v>274.95</v>
+      </c>
+      <c r="I110" s="1">
+        <v>543.45</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C111" s="1">
         <v>170.82</v>
@@ -3107,16 +4106,25 @@
       <c r="F111" s="1">
         <v>154.97</v>
       </c>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="G111" s="1">
+        <v>353.09</v>
+      </c>
+      <c r="H111" s="1">
+        <v>482.96</v>
+      </c>
+      <c r="I111" s="1">
+        <v>562.46</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C112" s="1">
         <v>527.67</v>
       </c>
       <c r="D112" s="1">
-        <v>64.87</v>
+        <v>64.87000000000003</v>
       </c>
       <c r="E112" s="1">
         <v>388.96</v>
@@ -3124,10 +4132,19 @@
       <c r="F112" s="1">
         <v>101.26</v>
       </c>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="G112" s="1">
+        <v>269.64</v>
+      </c>
+      <c r="H112" s="1">
+        <v>2353.42</v>
+      </c>
+      <c r="I112" s="1">
+        <v>1324.38</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C113" s="1">
         <v>232.62</v>
@@ -3141,10 +4158,19 @@
       <c r="F113" s="1">
         <v>552.0400000000001</v>
       </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H113" s="1">
+        <v>542.4200000000001</v>
+      </c>
+      <c r="I113" s="1">
+        <v>183.96</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C114" s="1">
         <v>-54.74000000000001</v>
@@ -3158,10 +4184,19 @@
       <c r="F114" s="1">
         <v>470.8200000000001</v>
       </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="G114" s="1">
+        <v>517.9200000000001</v>
+      </c>
+      <c r="H114" s="1">
+        <v>1439.58</v>
+      </c>
+      <c r="I114" s="1">
+        <v>462.96</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C115" s="1">
         <v>143.31</v>
@@ -3175,10 +4210,19 @@
       <c r="F115" s="1">
         <v>171.72</v>
       </c>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="G115" s="1">
+        <v>77.47</v>
+      </c>
+      <c r="H115" s="1">
+        <v>124.91</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C116" s="1">
         <v>-21.07</v>
@@ -3192,10 +4236,19 @@
       <c r="F116" s="1">
         <v>115.42</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="G116" s="1">
+        <v>931.9400000000001</v>
+      </c>
+      <c r="H116" s="1">
+        <v>1833.85</v>
+      </c>
+      <c r="I116" s="1">
+        <v>260.96</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C117" s="1">
         <v>493.78</v>
@@ -3209,16 +4262,25 @@
       <c r="F117" s="1">
         <v>220.12</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="G117" s="1">
+        <v>632.2</v>
+      </c>
+      <c r="H117" s="1">
+        <v>543.98</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C118" s="1">
         <v>2743.98</v>
       </c>
       <c r="D118" s="1">
-        <v>6091.289999999999</v>
+        <v>6091.290000000001</v>
       </c>
       <c r="E118" s="1">
         <v>7156.969999999998</v>
@@ -3226,10 +4288,19 @@
       <c r="F118" s="1">
         <v>1868.54</v>
       </c>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="G118" s="1">
+        <v>3026.7</v>
+      </c>
+      <c r="H118" s="1">
+        <v>5055.639999999999</v>
+      </c>
+      <c r="I118" s="1">
+        <v>5054.210000000002</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C119" s="1">
         <v>62.89</v>
@@ -3243,13 +4314,22 @@
       <c r="F119" s="1">
         <v>124.76</v>
       </c>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="G119" s="1">
+        <v>397.9400000000001</v>
+      </c>
+      <c r="H119" s="1">
+        <v>706.7900000000001</v>
+      </c>
+      <c r="I119" s="1">
+        <v>635.85</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C120" s="1">
-        <v>519.9400000000001</v>
+        <v>519.9399999999999</v>
       </c>
       <c r="D120" s="1">
         <v>1175.16</v>
@@ -3260,13 +4340,22 @@
       <c r="F120" s="1">
         <v>398.83</v>
       </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="G120" s="1">
+        <v>1173.45</v>
+      </c>
+      <c r="H120" s="1">
+        <v>1662.09</v>
+      </c>
+      <c r="I120" s="1">
+        <v>2017.27</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C121" s="1">
-        <v>875.9700000000001</v>
+        <v>875.97</v>
       </c>
       <c r="D121" s="1">
         <v>731.88</v>
@@ -3277,10 +4366,19 @@
       <c r="F121" s="1">
         <v>222.94</v>
       </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" s="1">
+        <v>770.8800000000001</v>
+      </c>
+      <c r="H121" s="1">
+        <v>334.76</v>
+      </c>
+      <c r="I121" s="1">
+        <v>699.97</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C122" s="1">
         <v>137.97</v>
@@ -3294,10 +4392,19 @@
       <c r="F122" s="1">
         <v>312.99</v>
       </c>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="G122" s="1">
+        <v>192.52</v>
+      </c>
+      <c r="H122" s="1">
+        <v>299.72</v>
+      </c>
+      <c r="I122" s="1">
+        <v>303.44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C123" s="1">
         <v>89.98</v>
@@ -3311,13 +4418,22 @@
       <c r="F123" s="1">
         <v>361.47</v>
       </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="G123" s="1">
+        <v>115.98</v>
+      </c>
+      <c r="H123" s="1">
+        <v>591.52</v>
+      </c>
+      <c r="I123" s="1">
+        <v>284.96</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C124" s="1">
-        <v>364.95</v>
+        <v>364.9499999999999</v>
       </c>
       <c r="D124" s="1">
         <v>99</v>
@@ -3328,10 +4444,19 @@
       <c r="F124" s="1">
         <v>70.98</v>
       </c>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="G124" s="1">
+        <v>415.18</v>
+      </c>
+      <c r="H124" s="1">
+        <v>366.76</v>
+      </c>
+      <c r="I124" s="1">
+        <v>974.1700000000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C125" s="1">
         <v>473.12</v>
@@ -3345,16 +4470,25 @@
       <c r="F125" s="1">
         <v>152.99</v>
       </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="G125" s="1">
+        <v>84.98</v>
+      </c>
+      <c r="H125" s="1">
+        <v>1770.47</v>
+      </c>
+      <c r="I125" s="1">
+        <v>1071.67</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C126" s="1">
         <v>120.49</v>
       </c>
       <c r="D126" s="1">
-        <v>458.8699999999999</v>
+        <v>458.87</v>
       </c>
       <c r="E126" s="1">
         <v>53.48</v>
@@ -3362,10 +4496,19 @@
       <c r="F126" s="1">
         <v>243.69</v>
       </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="G126" s="1">
+        <v>78.48</v>
+      </c>
+      <c r="H126" s="1">
+        <v>400.0300000000001</v>
+      </c>
+      <c r="I126" s="1">
+        <v>350.06</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C127" s="1">
         <v>198.96</v>
@@ -3377,18 +4520,27 @@
         <v>179</v>
       </c>
       <c r="F127" s="1">
-        <v>568.9300000000001</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+        <v>568.9299999999999</v>
+      </c>
+      <c r="G127" s="1">
+        <v>88.53999999999999</v>
+      </c>
+      <c r="H127" s="1">
+        <v>1004.73</v>
+      </c>
+      <c r="I127" s="1">
+        <v>409.26</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C128" s="1">
         <v>345.63</v>
       </c>
       <c r="D128" s="1">
-        <v>650.78</v>
+        <v>650.7800000000001</v>
       </c>
       <c r="E128" s="1">
         <v>548.12</v>
@@ -3396,30 +4548,48 @@
       <c r="F128" s="1">
         <v>718.7</v>
       </c>
-    </row>
-    <row r="129" spans="1:6">
+      <c r="G128" s="1">
+        <v>532.6500000000001</v>
+      </c>
+      <c r="H128" s="1">
+        <v>722.08</v>
+      </c>
+      <c r="I128" s="1">
+        <v>99.97</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C129" s="1">
-        <v>711.87</v>
+        <v>711.8700000000001</v>
       </c>
       <c r="D129" s="1">
-        <v>540.8800000000001</v>
+        <v>540.88</v>
       </c>
       <c r="E129" s="1">
-        <v>-245.66</v>
+        <v>-245.6599999999999</v>
       </c>
       <c r="F129" s="1">
         <v>1375.59</v>
       </c>
-    </row>
-    <row r="130" spans="1:6">
+      <c r="G129" s="1">
+        <v>711.71</v>
+      </c>
+      <c r="H129" s="1">
+        <v>1600.55</v>
+      </c>
+      <c r="I129" s="1">
+        <v>519.27</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C130" s="1">
-        <v>86.48999999999999</v>
+        <v>86.49000000000001</v>
       </c>
       <c r="D130" s="1">
         <v>79.88</v>
@@ -3430,10 +4600,19 @@
       <c r="F130" s="1">
         <v>169.96</v>
       </c>
-    </row>
-    <row r="131" spans="1:6">
+      <c r="G130" s="1">
+        <v>409.23</v>
+      </c>
+      <c r="H130" s="1">
+        <v>376.9300000000001</v>
+      </c>
+      <c r="I130" s="1">
+        <v>76.98999999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C131" s="1">
         <v>206.25</v>
@@ -3447,10 +4626,19 @@
       <c r="F131" s="1">
         <v>180.47</v>
       </c>
-    </row>
-    <row r="132" spans="1:6">
+      <c r="G131" s="1">
+        <v>93.66999999999999</v>
+      </c>
+      <c r="H131" s="1">
+        <v>88.97</v>
+      </c>
+      <c r="I131" s="1">
+        <v>93.97</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C132" s="1">
         <v>582.11</v>
@@ -3464,16 +4652,25 @@
       <c r="F132" s="1">
         <v>-69.69</v>
       </c>
-    </row>
-    <row r="133" spans="1:6">
+      <c r="G132" s="1">
+        <v>43.32</v>
+      </c>
+      <c r="H132" s="1">
+        <v>180.46</v>
+      </c>
+      <c r="I132" s="1">
+        <v>293.46</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C133" s="1">
-        <v>262.54</v>
+        <v>262.5400000000001</v>
       </c>
       <c r="D133" s="1">
-        <v>476.3700000000001</v>
+        <v>476.37</v>
       </c>
       <c r="E133" s="1">
         <v>580.59</v>
@@ -3481,10 +4678,19 @@
       <c r="F133" s="1">
         <v>226.72</v>
       </c>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="G133" s="1">
+        <v>793.54</v>
+      </c>
+      <c r="H133" s="1">
+        <v>584.6400000000001</v>
+      </c>
+      <c r="I133" s="1">
+        <v>957.0400000000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C134" s="1">
         <v>369.33</v>
@@ -3498,10 +4704,19 @@
       <c r="F134" s="1">
         <v>207.97</v>
       </c>
-    </row>
-    <row r="135" spans="1:6">
+      <c r="G134" s="1">
+        <v>139.99</v>
+      </c>
+      <c r="H134" s="1">
+        <v>213.46</v>
+      </c>
+      <c r="I134" s="1">
+        <v>415.53</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C135" s="1">
         <v>324.88</v>
@@ -3515,10 +4730,19 @@
       <c r="F135" s="1">
         <v>175.97</v>
       </c>
-    </row>
-    <row r="136" spans="1:6">
+      <c r="G135" s="1">
+        <v>1137.16</v>
+      </c>
+      <c r="H135" s="1">
+        <v>503.61</v>
+      </c>
+      <c r="I135" s="1">
+        <v>1936.08</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C136" s="1">
         <v>437.53</v>
@@ -3532,13 +4756,22 @@
       <c r="F136" s="1">
         <v>96.98</v>
       </c>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="G136" s="1">
+        <v>101.97</v>
+      </c>
+      <c r="H136" s="1">
+        <v>136.98</v>
+      </c>
+      <c r="I136" s="1">
+        <v>212.94</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C137" s="1">
-        <v>997.2099999999999</v>
+        <v>997.21</v>
       </c>
       <c r="D137" s="1">
         <v>516.76</v>
@@ -3549,10 +4782,19 @@
       <c r="F137" s="1">
         <v>1435.75</v>
       </c>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="G137" s="1">
+        <v>1293.73</v>
+      </c>
+      <c r="H137" s="1">
+        <v>1414.23</v>
+      </c>
+      <c r="I137" s="1">
+        <v>2612.34</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C138" s="1">
         <v>490.24</v>
@@ -3566,10 +4808,19 @@
       <c r="F138" s="1">
         <v>502.89</v>
       </c>
-    </row>
-    <row r="139" spans="1:6">
+      <c r="G138" s="1">
+        <v>484.45</v>
+      </c>
+      <c r="H138" s="1">
+        <v>717.34</v>
+      </c>
+      <c r="I138" s="1">
+        <v>1042.32</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C139" s="1">
         <v>48.94</v>
@@ -3578,15 +4829,24 @@
         <v>116.93</v>
       </c>
       <c r="E139" s="1">
-        <v>436.65</v>
+        <v>436.6500000000001</v>
       </c>
       <c r="F139" s="1">
-        <v>408.4</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
+        <v>408.4000000000001</v>
+      </c>
+      <c r="G139" s="1">
+        <v>597.9</v>
+      </c>
+      <c r="H139" s="1">
+        <v>780.04</v>
+      </c>
+      <c r="I139" s="1">
+        <v>875.85</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C140" s="1">
         <v>517.38</v>
@@ -3600,10 +4860,19 @@
       <c r="F140" s="1">
         <v>1649.93</v>
       </c>
-    </row>
-    <row r="141" spans="1:6">
+      <c r="G140" s="1">
+        <v>874.63</v>
+      </c>
+      <c r="H140" s="1">
+        <v>2363.5</v>
+      </c>
+      <c r="I140" s="1">
+        <v>1175.24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C141" s="1">
         <v>407.34</v>
@@ -3617,10 +4886,19 @@
       <c r="F141" s="1">
         <v>882.9299999999999</v>
       </c>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="G141" s="1">
+        <v>1184.29</v>
+      </c>
+      <c r="H141" s="1">
+        <v>1044.66</v>
+      </c>
+      <c r="I141" s="1">
+        <v>952.0500000000002</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C142" s="1">
         <v>435.95</v>
@@ -3634,10 +4912,19 @@
       <c r="F142" s="1">
         <v>34.99</v>
       </c>
-    </row>
-    <row r="143" spans="1:6">
+      <c r="G142" s="1">
+        <v>170.04</v>
+      </c>
+      <c r="H142" s="1">
+        <v>1078.51</v>
+      </c>
+      <c r="I142" s="1">
+        <v>872.96</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C143" s="1">
         <v>93.98</v>
@@ -3651,10 +4938,19 @@
       <c r="F143" s="1">
         <v>483.83</v>
       </c>
-    </row>
-    <row r="144" spans="1:6">
+      <c r="G143" s="1">
+        <v>158.97</v>
+      </c>
+      <c r="H143" s="1">
+        <v>555.1799999999999</v>
+      </c>
+      <c r="I143" s="1">
+        <v>398.28</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C144" s="1">
         <v>114.96</v>
@@ -3668,10 +4964,19 @@
       <c r="F144" s="1">
         <v>725.6700000000001</v>
       </c>
-    </row>
-    <row r="145" spans="1:6">
+      <c r="G144" s="1">
+        <v>634.0599999999999</v>
+      </c>
+      <c r="H144" s="1">
+        <v>1253.02</v>
+      </c>
+      <c r="I144" s="1">
+        <v>1054.03</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C145" s="1">
         <v>171.96</v>
@@ -3685,10 +4990,19 @@
       <c r="F145" s="1">
         <v>183.36</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
+      <c r="G145" s="1">
+        <v>332.46</v>
+      </c>
+      <c r="H145" s="1">
+        <v>500.9400000000001</v>
+      </c>
+      <c r="I145" s="1">
+        <v>333.45</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C146" s="1">
         <v>92.98</v>
@@ -3702,10 +5016,19 @@
       <c r="F146" s="1">
         <v>542.9300000000001</v>
       </c>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="G146" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H146" s="1">
+        <v>1160.13</v>
+      </c>
+      <c r="I146" s="1">
+        <v>1251.98</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C147" s="1">
         <v>336.96</v>
@@ -3717,12 +5040,21 @@
         <v>31.66</v>
       </c>
       <c r="F147" s="1">
-        <v>431.3099999999999</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
+        <v>431.31</v>
+      </c>
+      <c r="G147" s="1">
+        <v>246.17</v>
+      </c>
+      <c r="H147" s="1">
+        <v>345.73</v>
+      </c>
+      <c r="I147" s="1">
+        <v>384.4400000000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C148" s="1">
         <v>112.57</v>
@@ -3736,30 +5068,48 @@
       <c r="F148" s="1">
         <v>32.99</v>
       </c>
-    </row>
-    <row r="149" spans="1:6">
+      <c r="G148" s="1">
+        <v>937.9900000000001</v>
+      </c>
+      <c r="H148" s="1">
+        <v>1843.26</v>
+      </c>
+      <c r="I148" s="1">
+        <v>692.39</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C149" s="1">
         <v>1613.02</v>
       </c>
       <c r="D149" s="1">
-        <v>874.8600000000001</v>
+        <v>874.86</v>
       </c>
       <c r="E149" s="1">
-        <v>349.82</v>
+        <v>349.8199999999999</v>
       </c>
       <c r="F149" s="1">
-        <v>827.99</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
+        <v>827.9900000000001</v>
+      </c>
+      <c r="G149" s="1">
+        <v>86.35999999999997</v>
+      </c>
+      <c r="H149" s="1">
+        <v>1341.88</v>
+      </c>
+      <c r="I149" s="1">
+        <v>670.7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D150" s="1">
         <v>19.99</v>
@@ -3770,10 +5120,19 @@
       <c r="F150" s="1">
         <v>309.94</v>
       </c>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="G150" s="1">
+        <v>128.47</v>
+      </c>
+      <c r="H150" s="1">
+        <v>335.08</v>
+      </c>
+      <c r="I150" s="1">
+        <v>443.15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C151" s="1">
         <v>745.6600000000001</v>
@@ -3787,10 +5146,19 @@
       <c r="F151" s="1">
         <v>376.95</v>
       </c>
-    </row>
-    <row r="152" spans="1:6">
+      <c r="G151" s="1">
+        <v>218.34</v>
+      </c>
+      <c r="H151" s="1">
+        <v>2218.24</v>
+      </c>
+      <c r="I151" s="1">
+        <v>853.35</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C152" s="1">
         <v>334.68</v>
@@ -3802,15 +5170,24 @@
         <v>302.92</v>
       </c>
       <c r="F152" s="1">
-        <v>504.14</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
+        <v>504.1400000000001</v>
+      </c>
+      <c r="G152" s="1">
+        <v>425.41</v>
+      </c>
+      <c r="H152" s="1">
+        <v>727.89</v>
+      </c>
+      <c r="I152" s="1">
+        <v>812.36</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D153" s="1">
         <v>293.97</v>
@@ -3821,10 +5198,19 @@
       <c r="F153" s="1">
         <v>279</v>
       </c>
-    </row>
-    <row r="154" spans="1:6">
+      <c r="G153" s="1">
+        <v>397.16</v>
+      </c>
+      <c r="H153" s="1">
+        <v>876.0300000000001</v>
+      </c>
+      <c r="I153" s="1">
+        <v>235.93</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C154" s="1">
         <v>489.05</v>
@@ -3838,30 +5224,48 @@
       <c r="F154" s="1">
         <v>688.6</v>
       </c>
-    </row>
-    <row r="155" spans="1:6">
+      <c r="G154" s="1">
+        <v>749.3900000000001</v>
+      </c>
+      <c r="H154" s="1">
+        <v>1683.87</v>
+      </c>
+      <c r="I154" s="1">
+        <v>1277.94</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C155" s="1">
         <v>1417.91</v>
       </c>
       <c r="D155" s="1">
-        <v>991.02</v>
+        <v>991.0200000000001</v>
       </c>
       <c r="E155" s="1">
         <v>2016.94</v>
       </c>
       <c r="F155" s="1">
-        <v>580.9100000000001</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
+        <v>580.91</v>
+      </c>
+      <c r="G155" s="1">
+        <v>1207.02</v>
+      </c>
+      <c r="H155" s="1">
+        <v>2194.98</v>
+      </c>
+      <c r="I155" s="1">
+        <v>912.8099999999999</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C156" s="1">
-        <v>630.8499999999999</v>
+        <v>630.85</v>
       </c>
       <c r="D156" s="1">
         <v>328</v>
@@ -3872,13 +5276,22 @@
       <c r="F156" s="1">
         <v>681.96</v>
       </c>
-    </row>
-    <row r="157" spans="1:6">
+      <c r="G156" s="1">
+        <v>382.07</v>
+      </c>
+      <c r="H156" s="1">
+        <v>1183.27</v>
+      </c>
+      <c r="I156" s="1">
+        <v>926.9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C157" s="1">
-        <v>507.83</v>
+        <v>507.8299999999999</v>
       </c>
       <c r="D157" s="1">
         <v>310.97</v>
@@ -3889,10 +5302,19 @@
       <c r="F157" s="1">
         <v>172.09</v>
       </c>
-    </row>
-    <row r="158" spans="1:6">
+      <c r="G157" s="1">
+        <v>370.36</v>
+      </c>
+      <c r="H157" s="1">
+        <v>1064.84</v>
+      </c>
+      <c r="I157" s="1">
+        <v>737.63</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C158" s="1">
         <v>-50.49000000000001</v>
@@ -3901,15 +5323,24 @@
         <v>684.53</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F158" s="1">
         <v>140.76</v>
       </c>
-    </row>
-    <row r="159" spans="1:6">
+      <c r="G158" s="1">
+        <v>359.96</v>
+      </c>
+      <c r="H158" s="1">
+        <v>702.6900000000001</v>
+      </c>
+      <c r="I158" s="1">
+        <v>651.4000000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C159" s="1">
         <v>306.99</v>
@@ -3921,12 +5352,21 @@
         <v>680.9299999999999</v>
       </c>
       <c r="F159" s="1">
-        <v>550.4399999999999</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
+        <v>550.4400000000001</v>
+      </c>
+      <c r="G159" s="1">
+        <v>534.4300000000001</v>
+      </c>
+      <c r="H159" s="1">
+        <v>1135.64</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C160" s="1">
         <v>63.97</v>
@@ -3940,10 +5380,19 @@
       <c r="F160" s="1">
         <v>1172</v>
       </c>
-    </row>
-    <row r="161" spans="1:6">
+      <c r="G160" s="1">
+        <v>631.3200000000001</v>
+      </c>
+      <c r="H160" s="1">
+        <v>796.9100000000001</v>
+      </c>
+      <c r="I160" s="1">
+        <v>1301.52</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C161" s="1">
         <v>1939.74</v>
@@ -3957,10 +5406,19 @@
       <c r="F161" s="1">
         <v>409.06</v>
       </c>
-    </row>
-    <row r="162" spans="1:6">
+      <c r="G161" s="1">
+        <v>1118.05</v>
+      </c>
+      <c r="H161" s="1">
+        <v>833.3700000000001</v>
+      </c>
+      <c r="I161" s="1">
+        <v>1882.53</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C162" s="1">
         <v>241.96</v>
@@ -3974,13 +5432,22 @@
       <c r="F162" s="1">
         <v>196.48</v>
       </c>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="G162" s="1">
+        <v>221.99</v>
+      </c>
+      <c r="H162" s="1">
+        <v>223.47</v>
+      </c>
+      <c r="I162" s="1">
+        <v>178.44</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C163" s="1">
-        <v>87.47999999999999</v>
+        <v>87.48</v>
       </c>
       <c r="D163" s="1">
         <v>180.77</v>
@@ -3991,33 +5458,51 @@
       <c r="F163" s="1">
         <v>762.6900000000001</v>
       </c>
-    </row>
-    <row r="164" spans="1:6">
+      <c r="G163" s="1">
+        <v>246.06</v>
+      </c>
+      <c r="H163" s="1">
+        <v>734.1900000000001</v>
+      </c>
+      <c r="I163" s="1">
+        <v>19.95000000000001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C164" s="1">
         <v>218.23</v>
       </c>
       <c r="D164" s="1">
-        <v>79.98000000000002</v>
+        <v>79.98</v>
       </c>
       <c r="E164" s="1">
         <v>189.97</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G164" s="1">
+        <v>25.49</v>
+      </c>
+      <c r="H164" s="1">
+        <v>160.47</v>
+      </c>
+      <c r="I164" s="1">
+        <v>175.47</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C165" s="1">
         <v>597.49</v>
       </c>
       <c r="D165" s="1">
-        <v>478.8100000000001</v>
+        <v>478.81</v>
       </c>
       <c r="E165" s="1">
         <v>303.64</v>
@@ -4025,10 +5510,19 @@
       <c r="F165" s="1">
         <v>172.47</v>
       </c>
-    </row>
-    <row r="166" spans="1:6">
+      <c r="G165" s="1">
+        <v>669.6400000000001</v>
+      </c>
+      <c r="H165" s="1">
+        <v>1434.26</v>
+      </c>
+      <c r="I165" s="1">
+        <v>2073.58</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C166" s="1">
         <v>195.95</v>
@@ -4042,10 +5536,19 @@
       <c r="F166" s="1">
         <v>553.49</v>
       </c>
-    </row>
-    <row r="167" spans="1:6">
+      <c r="G166" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="H166" s="1">
+        <v>1397.24</v>
+      </c>
+      <c r="I166" s="1">
+        <v>270.36</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C167" s="1">
         <v>2422.389999999999</v>
@@ -4059,13 +5562,22 @@
       <c r="F167" s="1">
         <v>3611.549999999999</v>
       </c>
-    </row>
-    <row r="168" spans="1:6">
+      <c r="G167" s="1">
+        <v>4216.01</v>
+      </c>
+      <c r="H167" s="1">
+        <v>5260.170000000001</v>
+      </c>
+      <c r="I167" s="1">
+        <v>5178.57</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D168" s="1">
         <v>418.0700000000001</v>
@@ -4076,10 +5588,19 @@
       <c r="F168" s="1">
         <v>548.78</v>
       </c>
-    </row>
-    <row r="169" spans="1:6">
+      <c r="G168" s="1">
+        <v>566.01</v>
+      </c>
+      <c r="H168" s="1">
+        <v>762.4</v>
+      </c>
+      <c r="I168" s="1">
+        <v>94.98999999999999</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C169" s="1">
         <v>1148.62</v>
@@ -4093,10 +5614,19 @@
       <c r="F169" s="1">
         <v>1059.67</v>
       </c>
-    </row>
-    <row r="170" spans="1:6">
+      <c r="G169" s="1">
+        <v>963.0199999999999</v>
+      </c>
+      <c r="H169" s="1">
+        <v>3445.309999999999</v>
+      </c>
+      <c r="I169" s="1">
+        <v>1500.6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C170" s="1">
         <v>86.69</v>
@@ -4105,18 +5635,27 @@
         <v>523.9300000000001</v>
       </c>
       <c r="E170" s="1">
-        <v>445.8200000000001</v>
+        <v>445.82</v>
       </c>
       <c r="F170" s="1">
         <v>274.44</v>
       </c>
-    </row>
-    <row r="171" spans="1:6">
+      <c r="G170" s="1">
+        <v>21.49</v>
+      </c>
+      <c r="H170" s="1">
+        <v>87.69</v>
+      </c>
+      <c r="I170" s="1">
+        <v>465.93</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C171" s="1">
-        <v>225.88</v>
+        <v>225.8800000000001</v>
       </c>
       <c r="D171" s="1">
         <v>388.74</v>
@@ -4125,12 +5664,21 @@
         <v>234.53</v>
       </c>
       <c r="F171" s="1">
-        <v>921.87</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
+        <v>921.8700000000001</v>
+      </c>
+      <c r="G171" s="1">
+        <v>154.97</v>
+      </c>
+      <c r="H171" s="1">
+        <v>983.13</v>
+      </c>
+      <c r="I171" s="1">
+        <v>756.9900000000001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C172" s="1">
         <v>714.22</v>
@@ -4144,10 +5692,19 @@
       <c r="F172" s="1">
         <v>164.96</v>
       </c>
-    </row>
-    <row r="173" spans="1:6">
+      <c r="G172" s="1">
+        <v>540.28</v>
+      </c>
+      <c r="H172" s="1">
+        <v>720.49</v>
+      </c>
+      <c r="I172" s="1">
+        <v>890.0500000000002</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C173" s="1">
         <v>1479.2</v>
@@ -4161,10 +5718,19 @@
       <c r="F173" s="1">
         <v>1145.97</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
+      <c r="G173" s="1">
+        <v>305.94</v>
+      </c>
+      <c r="H173" s="1">
+        <v>1805.87</v>
+      </c>
+      <c r="I173" s="1">
+        <v>937.41</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C174" s="1">
         <v>164.94</v>
@@ -4178,10 +5744,19 @@
       <c r="F174" s="1">
         <v>698.25</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
+      <c r="G174" s="1">
+        <v>891.1</v>
+      </c>
+      <c r="H174" s="1">
+        <v>345.56</v>
+      </c>
+      <c r="I174" s="1">
+        <v>478.1800000000001</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C175" s="1">
         <v>385.07</v>
@@ -4195,10 +5770,19 @@
       <c r="F175" s="1">
         <v>825.28</v>
       </c>
-    </row>
-    <row r="176" spans="1:6">
+      <c r="G175" s="1">
+        <v>434.49</v>
+      </c>
+      <c r="H175" s="1">
+        <v>691.0200000000001</v>
+      </c>
+      <c r="I175" s="1">
+        <v>568.42</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C176" s="1">
         <v>310.26</v>
@@ -4207,15 +5791,24 @@
         <v>68.98999999999999</v>
       </c>
       <c r="E176" s="1">
-        <v>785.5400000000001</v>
+        <v>785.54</v>
       </c>
       <c r="F176" s="1">
         <v>168.98</v>
       </c>
-    </row>
-    <row r="177" spans="1:6">
+      <c r="G176" s="1">
+        <v>606.22</v>
+      </c>
+      <c r="H176" s="1">
+        <v>776.61</v>
+      </c>
+      <c r="I176" s="1">
+        <v>609.91</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C177" s="1">
         <v>119.97</v>
@@ -4229,10 +5822,19 @@
       <c r="F177" s="1">
         <v>171.87</v>
       </c>
-    </row>
-    <row r="178" spans="1:6">
+      <c r="G177" s="1">
+        <v>142.18</v>
+      </c>
+      <c r="H177" s="1">
+        <v>506.5400000000001</v>
+      </c>
+      <c r="I177" s="1">
+        <v>250.26</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C178" s="1">
         <v>314.11</v>
@@ -4246,10 +5848,19 @@
       <c r="F178" s="1">
         <v>680.37</v>
       </c>
-    </row>
-    <row r="179" spans="1:6">
+      <c r="G178" s="1">
+        <v>356.95</v>
+      </c>
+      <c r="H178" s="1">
+        <v>197.96</v>
+      </c>
+      <c r="I178" s="1">
+        <v>655.4200000000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C179" s="1">
         <v>104.66</v>
@@ -4263,10 +5874,19 @@
       <c r="F179" s="1">
         <v>32.58</v>
       </c>
-    </row>
-    <row r="180" spans="1:6">
+      <c r="G179" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H179" s="1">
+        <v>509.3000000000001</v>
+      </c>
+      <c r="I179" s="1">
+        <v>173.57</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C180" s="1">
         <v>359.84</v>
@@ -4280,10 +5900,19 @@
       <c r="F180" s="1">
         <v>534.37</v>
       </c>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="G180" s="1">
+        <v>597.26</v>
+      </c>
+      <c r="H180" s="1">
+        <v>1309.74</v>
+      </c>
+      <c r="I180" s="1">
+        <v>315.72</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C181" s="1">
         <v>897.2900000000001</v>
@@ -4297,10 +5926,19 @@
       <c r="F181" s="1">
         <v>149.14</v>
       </c>
-    </row>
-    <row r="182" spans="1:6">
+      <c r="G181" s="1">
+        <v>847.0700000000001</v>
+      </c>
+      <c r="H181" s="1">
+        <v>1166.25</v>
+      </c>
+      <c r="I181" s="1">
+        <v>1107.71</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C182" s="1">
         <v>428.96</v>
@@ -4309,21 +5947,30 @@
         <v>193.5</v>
       </c>
       <c r="E182" s="1">
-        <v>683.6099999999999</v>
+        <v>683.6100000000001</v>
       </c>
       <c r="F182" s="1">
         <v>602.98</v>
       </c>
-    </row>
-    <row r="183" spans="1:6">
+      <c r="G182" s="1">
+        <v>280.44</v>
+      </c>
+      <c r="H182" s="1">
+        <v>269.15</v>
+      </c>
+      <c r="I182" s="1">
+        <v>132.21</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E183" s="1">
         <v>143.91</v>
@@ -4331,10 +5978,19 @@
       <c r="F183" s="1">
         <v>112.97</v>
       </c>
-    </row>
-    <row r="184" spans="1:6">
+      <c r="G183" s="1">
+        <v>79.48999999999999</v>
+      </c>
+      <c r="H183" s="1">
+        <v>344.94</v>
+      </c>
+      <c r="I183" s="1">
+        <v>430.4000000000001</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C184" s="1">
         <v>233.22</v>
@@ -4348,10 +6004,19 @@
       <c r="F184" s="1">
         <v>806.4400000000001</v>
       </c>
-    </row>
-    <row r="185" spans="1:6">
+      <c r="G184" s="1">
+        <v>879.59</v>
+      </c>
+      <c r="H184" s="1">
+        <v>711.6</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C185" s="1">
         <v>1218.05</v>
@@ -4365,33 +6030,51 @@
       <c r="F185" s="1">
         <v>898.99</v>
       </c>
-    </row>
-    <row r="186" spans="1:6">
+      <c r="G185" s="1">
+        <v>580.53</v>
+      </c>
+      <c r="H185" s="1">
+        <v>1218.06</v>
+      </c>
+      <c r="I185" s="1">
+        <v>1992.64</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C186" s="1">
         <v>87.52</v>
       </c>
       <c r="D186" s="1">
-        <v>690.2900000000001</v>
+        <v>690.29</v>
       </c>
       <c r="E186" s="1">
-        <v>605.0200000000001</v>
+        <v>605.02</v>
       </c>
       <c r="F186" s="1">
         <v>865.1799999999999</v>
       </c>
-    </row>
-    <row r="187" spans="1:6">
+      <c r="G186" s="1">
+        <v>224.96</v>
+      </c>
+      <c r="H186" s="1">
+        <v>397.96</v>
+      </c>
+      <c r="I186" s="1">
+        <v>573.08</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C187" s="1">
         <v>247.23</v>
       </c>
       <c r="D187" s="1">
-        <v>503.1900000000001</v>
+        <v>503.19</v>
       </c>
       <c r="E187" s="1">
         <v>229.96</v>
@@ -4399,10 +6082,19 @@
       <c r="F187" s="1">
         <v>485.72</v>
       </c>
-    </row>
-    <row r="188" spans="1:6">
+      <c r="G187" s="1">
+        <v>918.96</v>
+      </c>
+      <c r="H187" s="1">
+        <v>1049.97</v>
+      </c>
+      <c r="I187" s="1">
+        <v>250.46</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C188" s="1">
         <v>1908.19</v>
@@ -4416,10 +6108,19 @@
       <c r="F188" s="1">
         <v>1037.15</v>
       </c>
-    </row>
-    <row r="189" spans="1:6">
+      <c r="G188" s="1">
+        <v>2150.42</v>
+      </c>
+      <c r="H188" s="1">
+        <v>3301.649999999999</v>
+      </c>
+      <c r="I188" s="1">
+        <v>3652.359999999999</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C189" s="1">
         <v>1221.86</v>
@@ -4433,13 +6134,22 @@
       <c r="F189" s="1">
         <v>162.65</v>
       </c>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="G189" s="1">
+        <v>729.0700000000001</v>
+      </c>
+      <c r="H189" s="1">
+        <v>2334.53</v>
+      </c>
+      <c r="I189" s="1">
+        <v>669.0400000000001</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C190" s="1">
-        <v>558.2</v>
+        <v>558.1999999999999</v>
       </c>
       <c r="D190" s="1">
         <v>94.52000000000001</v>
@@ -4450,10 +6160,19 @@
       <c r="F190" s="1">
         <v>209.43</v>
       </c>
-    </row>
-    <row r="191" spans="1:6">
+      <c r="G190" s="1">
+        <v>107.76</v>
+      </c>
+      <c r="H190" s="1">
+        <v>1030.53</v>
+      </c>
+      <c r="I190" s="1">
+        <v>579.4299999999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C191" s="1">
         <v>399.41</v>
@@ -4467,10 +6186,19 @@
       <c r="F191" s="1">
         <v>335.42</v>
       </c>
-    </row>
-    <row r="192" spans="1:6">
+      <c r="G191" s="1">
+        <v>1065.11</v>
+      </c>
+      <c r="H191" s="1">
+        <v>864.09</v>
+      </c>
+      <c r="I191" s="1">
+        <v>232.54</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C192" s="1">
         <v>230.49</v>
@@ -4482,12 +6210,21 @@
         <v>236.38</v>
       </c>
       <c r="F192" s="1">
-        <v>631.2199999999999</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
+        <v>631.22</v>
+      </c>
+      <c r="G192" s="1">
+        <v>1141.08</v>
+      </c>
+      <c r="H192" s="1">
+        <v>822.2700000000001</v>
+      </c>
+      <c r="I192" s="1">
+        <v>1208.38</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C193" s="1">
         <v>65.89</v>
@@ -4499,18 +6236,27 @@
         <v>399.08</v>
       </c>
       <c r="F193" s="1">
-        <v>59.05</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
+        <v>59.05000000000003</v>
+      </c>
+      <c r="G193" s="1">
+        <v>912.0799999999999</v>
+      </c>
+      <c r="H193" s="1">
+        <v>727.95</v>
+      </c>
+      <c r="I193" s="1">
+        <v>322.39</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C194" s="1">
         <v>1091.3</v>
       </c>
       <c r="D194" s="1">
-        <v>993.6300000000001</v>
+        <v>993.6300000000002</v>
       </c>
       <c r="E194" s="1">
         <v>1756.31</v>
@@ -4518,10 +6264,19 @@
       <c r="F194" s="1">
         <v>2301.43</v>
       </c>
-    </row>
-    <row r="195" spans="1:6">
+      <c r="G194" s="1">
+        <v>3099.04</v>
+      </c>
+      <c r="H194" s="1">
+        <v>3361.7</v>
+      </c>
+      <c r="I194" s="1">
+        <v>2820.97</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C195" s="1">
         <v>1132.39</v>
@@ -4535,10 +6290,19 @@
       <c r="F195" s="1">
         <v>1310.85</v>
       </c>
-    </row>
-    <row r="196" spans="1:6">
+      <c r="G195" s="1">
+        <v>367.13</v>
+      </c>
+      <c r="H195" s="1">
+        <v>1562.39</v>
+      </c>
+      <c r="I195" s="1">
+        <v>698.98</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C196" s="1">
         <v>194.96</v>
@@ -4552,10 +6316,19 @@
       <c r="F196" s="1">
         <v>285.57</v>
       </c>
-    </row>
-    <row r="197" spans="1:6">
+      <c r="G196" s="1">
+        <v>432.05</v>
+      </c>
+      <c r="H196" s="1">
+        <v>598.75</v>
+      </c>
+      <c r="I196" s="1">
+        <v>830.4400000000001</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C197" s="1">
         <v>553.1900000000001</v>
@@ -4564,15 +6337,24 @@
         <v>1807.87</v>
       </c>
       <c r="E197" s="1">
-        <v>867.39</v>
+        <v>867.3900000000001</v>
       </c>
       <c r="F197" s="1">
         <v>2188.92</v>
       </c>
-    </row>
-    <row r="198" spans="1:6">
+      <c r="G197" s="1">
+        <v>2081.64</v>
+      </c>
+      <c r="H197" s="1">
+        <v>856.41</v>
+      </c>
+      <c r="I197" s="1">
+        <v>1157.83</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C198" s="1">
         <v>615.6</v>
@@ -4586,44 +6368,71 @@
       <c r="F198" s="1">
         <v>526.0799999999999</v>
       </c>
-    </row>
-    <row r="199" spans="1:6">
+      <c r="G198" s="1">
+        <v>474.99</v>
+      </c>
+      <c r="H198" s="1">
+        <v>651.96</v>
+      </c>
+      <c r="I198" s="1">
+        <v>794.46</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C199" s="1">
         <v>181.09</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F199" s="1">
         <v>74.78</v>
       </c>
-    </row>
-    <row r="200" spans="1:6">
+      <c r="G199" s="1">
+        <v>178.98</v>
+      </c>
+      <c r="H199" s="1">
+        <v>274.95</v>
+      </c>
+      <c r="I199" s="1">
+        <v>228.95</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C200" s="1">
         <v>209.95</v>
       </c>
       <c r="D200" s="1">
-        <v>25.28999999999999</v>
+        <v>25.29</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F200" s="1">
         <v>438.45</v>
       </c>
-    </row>
-    <row r="201" spans="1:6">
+      <c r="G200" s="1">
+        <v>218.47</v>
+      </c>
+      <c r="H200" s="1">
+        <v>975.9900000000001</v>
+      </c>
+      <c r="I200" s="1">
+        <v>734.3200000000001</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C201" s="1">
         <v>1512.39</v>
@@ -4637,27 +6446,45 @@
       <c r="F201" s="1">
         <v>1814.31</v>
       </c>
-    </row>
-    <row r="202" spans="1:6">
+      <c r="G201" s="1">
+        <v>518.1</v>
+      </c>
+      <c r="H201" s="1">
+        <v>2828.909999999999</v>
+      </c>
+      <c r="I201" s="1">
+        <v>3358.969999999999</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C202" s="1">
         <v>243.96</v>
       </c>
       <c r="D202" s="1">
-        <v>865.0500000000002</v>
+        <v>865.05</v>
       </c>
       <c r="E202" s="1">
         <v>1250.68</v>
       </c>
       <c r="F202" s="1">
-        <v>799.51</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
+        <v>799.5100000000001</v>
+      </c>
+      <c r="G202" s="1">
+        <v>1057.78</v>
+      </c>
+      <c r="H202" s="1">
+        <v>666.35</v>
+      </c>
+      <c r="I202" s="1">
+        <v>788.2300000000001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C203" s="1">
         <v>134.98</v>
@@ -4669,12 +6496,21 @@
         <v>539.65</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G203" s="1">
+        <v>-47.41</v>
+      </c>
+      <c r="H203" s="1">
+        <v>651.65</v>
+      </c>
+      <c r="I203" s="1">
+        <v>255.95</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C204" s="1">
         <v>181.05</v>
@@ -4686,12 +6522,21 @@
         <v>1054.95</v>
       </c>
       <c r="F204" s="1">
-        <v>554.91</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
+        <v>554.9100000000001</v>
+      </c>
+      <c r="G204" s="1">
+        <v>217.69</v>
+      </c>
+      <c r="H204" s="1">
+        <v>381.25</v>
+      </c>
+      <c r="I204" s="1">
+        <v>615.8200000000001</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C205" s="1">
         <v>304.98</v>
@@ -4703,12 +6548,21 @@
         <v>579.42</v>
       </c>
       <c r="F205" s="1">
-        <v>84.77000000000001</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
+        <v>84.77</v>
+      </c>
+      <c r="G205" s="1">
+        <v>749.1900000000001</v>
+      </c>
+      <c r="H205" s="1">
+        <v>76.66</v>
+      </c>
+      <c r="I205" s="1">
+        <v>188.26</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C206" s="1">
         <v>529.88</v>
@@ -4722,10 +6576,19 @@
       <c r="F206" s="1">
         <v>186.07</v>
       </c>
-    </row>
-    <row r="207" spans="1:6">
+      <c r="G206" s="1">
+        <v>502.45</v>
+      </c>
+      <c r="H206" s="1">
+        <v>1732.37</v>
+      </c>
+      <c r="I206" s="1">
+        <v>739.12</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C207" s="1">
         <v>238.92</v>
@@ -4737,18 +6600,27 @@
         <v>559.91</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G207" s="1">
+        <v>173.96</v>
+      </c>
+      <c r="H207" s="1">
+        <v>1677.41</v>
+      </c>
+      <c r="I207" s="1">
+        <v>527.9400000000001</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C208" s="1">
         <v>267.47</v>
       </c>
       <c r="D208" s="1">
-        <v>417.43</v>
+        <v>417.4299999999999</v>
       </c>
       <c r="E208" s="1">
         <v>357.14</v>
@@ -4756,10 +6628,19 @@
       <c r="F208" s="1">
         <v>116.47</v>
       </c>
-    </row>
-    <row r="209" spans="1:6">
+      <c r="G208" s="1">
+        <v>76.98</v>
+      </c>
+      <c r="H208" s="1">
+        <v>583.72</v>
+      </c>
+      <c r="I208" s="1">
+        <v>818.5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C209" s="1">
         <v>52.48</v>
@@ -4768,18 +6649,27 @@
         <v>-132.08</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F209" s="1">
         <v>225.59</v>
       </c>
-    </row>
-    <row r="210" spans="1:6">
+      <c r="G209" s="1">
+        <v>209.97</v>
+      </c>
+      <c r="H209" s="1">
+        <v>668.24</v>
+      </c>
+      <c r="I209" s="1">
+        <v>471.41</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D210" s="1">
         <v>664.99</v>
@@ -4788,12 +6678,21 @@
         <v>109.99</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G210" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="H210" s="1">
+        <v>287.92</v>
+      </c>
+      <c r="I210" s="1">
+        <v>294.12</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C211" s="1">
         <v>354.96</v>
@@ -4807,10 +6706,19 @@
       <c r="F211" s="1">
         <v>220.99</v>
       </c>
-    </row>
-    <row r="212" spans="1:6">
+      <c r="G211" s="1">
+        <v>422.46</v>
+      </c>
+      <c r="H211" s="1">
+        <v>700.0400000000001</v>
+      </c>
+      <c r="I211" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C212" s="1">
         <v>279.96</v>
@@ -4824,10 +6732,19 @@
       <c r="F212" s="1">
         <v>414.94</v>
       </c>
-    </row>
-    <row r="213" spans="1:6">
+      <c r="G212" s="1">
+        <v>1102.11</v>
+      </c>
+      <c r="H212" s="1">
+        <v>673.97</v>
+      </c>
+      <c r="I212" s="1">
+        <v>854.8600000000001</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C213" s="1">
         <v>136.93</v>
@@ -4841,10 +6758,19 @@
       <c r="F213" s="1">
         <v>217.97</v>
       </c>
-    </row>
-    <row r="214" spans="1:6">
+      <c r="G213" s="1">
+        <v>230.94</v>
+      </c>
+      <c r="H213" s="1">
+        <v>429.94</v>
+      </c>
+      <c r="I213" s="1">
+        <v>210.46</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C214" s="1">
         <v>268.97</v>
@@ -4858,16 +6784,25 @@
       <c r="F214" s="1">
         <v>1387.51</v>
       </c>
-    </row>
-    <row r="215" spans="1:6">
+      <c r="G214" s="1">
+        <v>1024.46</v>
+      </c>
+      <c r="H214" s="1">
+        <v>3747.08</v>
+      </c>
+      <c r="I214" s="1">
+        <v>861.4400000000001</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C215" s="1">
         <v>103.85</v>
       </c>
       <c r="D215" s="1">
-        <v>521.9899999999999</v>
+        <v>521.99</v>
       </c>
       <c r="E215" s="1">
         <v>811.9100000000001</v>
@@ -4875,10 +6810,19 @@
       <c r="F215" s="1">
         <v>522.3299999999999</v>
       </c>
-    </row>
-    <row r="216" spans="1:6">
+      <c r="G215" s="1">
+        <v>541.4</v>
+      </c>
+      <c r="H215" s="1">
+        <v>725.59</v>
+      </c>
+      <c r="I215" s="1">
+        <v>1251.48</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C216" s="1">
         <v>411.46</v>
@@ -4892,13 +6836,22 @@
       <c r="F216" s="1">
         <v>457.11</v>
       </c>
-    </row>
-    <row r="217" spans="1:6">
+      <c r="G216" s="1">
+        <v>475.9000000000001</v>
+      </c>
+      <c r="H216" s="1">
+        <v>833.01</v>
+      </c>
+      <c r="I216" s="1">
+        <v>564.89</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C217" s="1">
-        <v>512.3099999999999</v>
+        <v>512.3100000000001</v>
       </c>
       <c r="D217" s="1">
         <v>104.99</v>
@@ -4909,10 +6862,19 @@
       <c r="F217" s="1">
         <v>89.97</v>
       </c>
-    </row>
-    <row r="218" spans="1:6">
+      <c r="G217" s="1">
+        <v>421.07</v>
+      </c>
+      <c r="H217" s="1">
+        <v>196.97</v>
+      </c>
+      <c r="I217" s="1">
+        <v>294.08</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C218" s="1">
         <v>451.95</v>
@@ -4921,15 +6883,24 @@
         <v>48.98</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F218" s="1">
         <v>625.87</v>
       </c>
-    </row>
-    <row r="219" spans="1:6">
+      <c r="G218" s="1">
+        <v>37.98</v>
+      </c>
+      <c r="H218" s="1">
+        <v>269.81</v>
+      </c>
+      <c r="I218" s="1">
+        <v>307.4300000000001</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C219" s="1">
         <v>59.98</v>
@@ -4943,10 +6914,19 @@
       <c r="F219" s="1">
         <v>149</v>
       </c>
-    </row>
-    <row r="220" spans="1:6">
+      <c r="G219" s="1">
+        <v>960.72</v>
+      </c>
+      <c r="H219" s="1">
+        <v>1443.57</v>
+      </c>
+      <c r="I219" s="1">
+        <v>305.47</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C220" s="1">
         <v>351.94</v>
@@ -4960,27 +6940,45 @@
       <c r="F220" s="1">
         <v>526.99</v>
       </c>
-    </row>
-    <row r="221" spans="1:6">
+      <c r="G220" s="1">
+        <v>54.99</v>
+      </c>
+      <c r="H220" s="1">
+        <v>756.6600000000001</v>
+      </c>
+      <c r="I220" s="1">
+        <v>994.85</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C221" s="1">
-        <v>546.0599999999999</v>
+        <v>546.0600000000001</v>
       </c>
       <c r="D221" s="1">
         <v>20.99</v>
       </c>
       <c r="E221" s="1">
-        <v>356.1799999999999</v>
+        <v>356.18</v>
       </c>
       <c r="F221" s="1">
         <v>714.9400000000001</v>
       </c>
-    </row>
-    <row r="222" spans="1:6">
+      <c r="G221" s="1">
+        <v>84.98</v>
+      </c>
+      <c r="H221" s="1">
+        <v>336.86</v>
+      </c>
+      <c r="I221" s="1">
+        <v>1040.37</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C222" s="1">
         <v>1257.74</v>
@@ -4994,10 +6992,19 @@
       <c r="F222" s="1">
         <v>711.72</v>
       </c>
-    </row>
-    <row r="223" spans="1:6">
+      <c r="G222" s="1">
+        <v>780.96</v>
+      </c>
+      <c r="H222" s="1">
+        <v>1030.48</v>
+      </c>
+      <c r="I222" s="1">
+        <v>947.5100000000001</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C223" s="1">
         <v>127.97</v>
@@ -5011,10 +7018,19 @@
       <c r="F223" s="1">
         <v>513.1900000000001</v>
       </c>
-    </row>
-    <row r="224" spans="1:6">
+      <c r="G223" s="1">
+        <v>80.47</v>
+      </c>
+      <c r="H223" s="1">
+        <v>732.5599999999999</v>
+      </c>
+      <c r="I223" s="1">
+        <v>871.09</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C224" s="1">
         <v>615.0599999999999</v>
@@ -5028,10 +7044,19 @@
       <c r="F224" s="1">
         <v>1124.02</v>
       </c>
-    </row>
-    <row r="225" spans="1:6">
+      <c r="G224" s="1">
+        <v>625.63</v>
+      </c>
+      <c r="H224" s="1">
+        <v>1661.86</v>
+      </c>
+      <c r="I224" s="1">
+        <v>339.96</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C225" s="1">
         <v>393.45</v>
@@ -5045,10 +7070,19 @@
       <c r="F225" s="1">
         <v>134.08</v>
       </c>
-    </row>
-    <row r="226" spans="1:6">
+      <c r="G225" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H225" s="1">
+        <v>14.04</v>
+      </c>
+      <c r="I225" s="1">
+        <v>523.1899999999999</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C226" s="1">
         <v>211.97</v>
@@ -5062,10 +7096,19 @@
       <c r="F226" s="1">
         <v>111.96</v>
       </c>
-    </row>
-    <row r="227" spans="1:6">
+      <c r="G226" s="1">
+        <v>288.63</v>
+      </c>
+      <c r="H226" s="1">
+        <v>616.33</v>
+      </c>
+      <c r="I226" s="1">
+        <v>857.6600000000001</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C227" s="1">
         <v>960.88</v>
@@ -5079,10 +7122,19 @@
       <c r="F227" s="1">
         <v>2644.36</v>
       </c>
-    </row>
-    <row r="228" spans="1:6">
+      <c r="G227" s="1">
+        <v>1093.6</v>
+      </c>
+      <c r="H227" s="1">
+        <v>3819.339999999999</v>
+      </c>
+      <c r="I227" s="1">
+        <v>1385.22</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C228" s="1">
         <v>125.49</v>
@@ -5091,15 +7143,24 @@
         <v>525.1900000000001</v>
       </c>
       <c r="E228" s="1">
-        <v>967.1400000000001</v>
+        <v>967.14</v>
       </c>
       <c r="F228" s="1">
         <v>672.47</v>
       </c>
-    </row>
-    <row r="229" spans="1:6">
+      <c r="G228" s="1">
+        <v>871.3800000000001</v>
+      </c>
+      <c r="H228" s="1">
+        <v>2632.669999999999</v>
+      </c>
+      <c r="I228" s="1">
+        <v>435.98</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C229" s="1">
         <v>37.9</v>
@@ -5113,10 +7174,19 @@
       <c r="F229" s="1">
         <v>291.27</v>
       </c>
-    </row>
-    <row r="230" spans="1:6">
+      <c r="G229" s="1">
+        <v>418.34</v>
+      </c>
+      <c r="H229" s="1">
+        <v>386.98</v>
+      </c>
+      <c r="I229" s="1">
+        <v>521.9100000000001</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C230" s="1">
         <v>208.38</v>
@@ -5130,10 +7200,19 @@
       <c r="F230" s="1">
         <v>135.07</v>
       </c>
-    </row>
-    <row r="231" spans="1:6">
+      <c r="G230" s="1">
+        <v>456.96</v>
+      </c>
+      <c r="H230" s="1">
+        <v>461.06</v>
+      </c>
+      <c r="I230" s="1">
+        <v>606.1700000000001</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C231" s="1">
         <v>23.99</v>
@@ -5147,16 +7226,25 @@
       <c r="F231" s="1">
         <v>28.49</v>
       </c>
-    </row>
-    <row r="232" spans="1:6">
+      <c r="G231" s="1">
+        <v>145.97</v>
+      </c>
+      <c r="H231" s="1">
+        <v>248.15</v>
+      </c>
+      <c r="I231" s="1">
+        <v>129.49</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C232" s="1">
         <v>234.06</v>
       </c>
       <c r="D232" s="1">
-        <v>343.88</v>
+        <v>343.8800000000001</v>
       </c>
       <c r="E232" s="1">
         <v>336.32</v>
@@ -5164,10 +7252,19 @@
       <c r="F232" s="1">
         <v>778.34</v>
       </c>
-    </row>
-    <row r="233" spans="1:6">
+      <c r="G232" s="1">
+        <v>371.6500000000001</v>
+      </c>
+      <c r="H232" s="1">
+        <v>1131.53</v>
+      </c>
+      <c r="I232" s="1">
+        <v>1140.46</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C233" s="1">
         <v>899.08</v>
@@ -5176,49 +7273,76 @@
         <v>473.69</v>
       </c>
       <c r="E233" s="1">
-        <v>466.37</v>
+        <v>466.3699999999999</v>
       </c>
       <c r="F233" s="1">
-        <v>964.17</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
+        <v>964.1700000000001</v>
+      </c>
+      <c r="G233" s="1">
+        <v>117.25</v>
+      </c>
+      <c r="H233" s="1">
+        <v>1089.98</v>
+      </c>
+      <c r="I233" s="1">
+        <v>987.96</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C234" s="1">
-        <v>413.0700000000001</v>
+        <v>413.07</v>
       </c>
       <c r="D234" s="1">
-        <v>498.3800000000001</v>
+        <v>498.38</v>
       </c>
       <c r="E234" s="1">
         <v>482.45</v>
       </c>
       <c r="F234" s="1">
-        <v>852.05</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
+        <v>852.0500000000002</v>
+      </c>
+      <c r="G234" s="1">
+        <v>980.51</v>
+      </c>
+      <c r="H234" s="1">
+        <v>1021.16</v>
+      </c>
+      <c r="I234" s="1">
+        <v>294.23</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C235" s="1">
-        <v>630.6199999999999</v>
+        <v>630.62</v>
       </c>
       <c r="D235" s="1">
-        <v>385.6800000000001</v>
+        <v>385.68</v>
       </c>
       <c r="E235" s="1">
-        <v>956.7700000000001</v>
+        <v>956.77</v>
       </c>
       <c r="F235" s="1">
         <v>692.77</v>
       </c>
-    </row>
-    <row r="236" spans="1:6">
+      <c r="G235" s="1">
+        <v>884.97</v>
+      </c>
+      <c r="H235" s="1">
+        <v>713.83</v>
+      </c>
+      <c r="I235" s="1">
+        <v>904.77</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C236" s="1">
         <v>447.46</v>
@@ -5232,10 +7356,19 @@
       <c r="F236" s="1">
         <v>126.14</v>
       </c>
-    </row>
-    <row r="237" spans="1:6">
+      <c r="G236" s="1">
+        <v>496.51</v>
+      </c>
+      <c r="H236" s="1">
+        <v>1269.05</v>
+      </c>
+      <c r="I236" s="1">
+        <v>306.08</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C237" s="1">
         <v>282.61</v>
@@ -5244,21 +7377,30 @@
         <v>315.97</v>
       </c>
       <c r="E237" s="1">
-        <v>378.3499999999999</v>
+        <v>378.35</v>
       </c>
       <c r="F237" s="1">
         <v>456.1900000000001</v>
       </c>
-    </row>
-    <row r="238" spans="1:6">
+      <c r="G237" s="1">
+        <v>764.9200000000001</v>
+      </c>
+      <c r="H237" s="1">
+        <v>840.87</v>
+      </c>
+      <c r="I237" s="1">
+        <v>1020.97</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C238" s="1">
         <v>131.94</v>
       </c>
       <c r="D238" s="1">
-        <v>676.6199999999999</v>
+        <v>676.62</v>
       </c>
       <c r="E238" s="1">
         <v>325.93</v>
@@ -5266,13 +7408,22 @@
       <c r="F238" s="1">
         <v>317.96</v>
       </c>
-    </row>
-    <row r="239" spans="1:6">
+      <c r="G238" s="1">
+        <v>838.63</v>
+      </c>
+      <c r="H238" s="1">
+        <v>508.8200000000001</v>
+      </c>
+      <c r="I238" s="1">
+        <v>349.71</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C239" s="1">
-        <v>34.98999999999999</v>
+        <v>34.99</v>
       </c>
       <c r="D239" s="1">
         <v>276.13</v>
@@ -5283,10 +7434,19 @@
       <c r="F239" s="1">
         <v>478.97</v>
       </c>
-    </row>
-    <row r="240" spans="1:6">
+      <c r="G239" s="1">
+        <v>515.4299999999999</v>
+      </c>
+      <c r="H239" s="1">
+        <v>356.42</v>
+      </c>
+      <c r="I239" s="1">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C240" s="1">
         <v>261.45</v>
@@ -5300,10 +7460,19 @@
       <c r="F240" s="1">
         <v>269.76</v>
       </c>
-    </row>
-    <row r="241" spans="1:6">
+      <c r="G240" s="1">
+        <v>386.63</v>
+      </c>
+      <c r="H240" s="1">
+        <v>418.3000000000001</v>
+      </c>
+      <c r="I240" s="1">
+        <v>39.48</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C241" s="1">
         <v>77.48</v>
@@ -5317,33 +7486,51 @@
       <c r="F241" s="1">
         <v>206.97</v>
       </c>
-    </row>
-    <row r="242" spans="1:6">
+      <c r="G241" s="1">
+        <v>277.71</v>
+      </c>
+      <c r="H241" s="1">
+        <v>438.36</v>
+      </c>
+      <c r="I241" s="1">
+        <v>386.58</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C242" s="1">
-        <v>866.38</v>
+        <v>866.3800000000001</v>
       </c>
       <c r="D242" s="1">
-        <v>343.93</v>
+        <v>343.9299999999999</v>
       </c>
       <c r="E242" s="1">
         <v>871.01</v>
       </c>
       <c r="F242" s="1">
-        <v>339.0700000000001</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
+        <v>339.07</v>
+      </c>
+      <c r="G242" s="1">
+        <v>841.85</v>
+      </c>
+      <c r="H242" s="1">
+        <v>1197.08</v>
+      </c>
+      <c r="I242" s="1">
+        <v>1028.06</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C243" s="1">
         <v>1017.25</v>
       </c>
       <c r="D243" s="1">
-        <v>697.4</v>
+        <v>697.4000000000001</v>
       </c>
       <c r="E243" s="1">
         <v>784.1600000000001</v>
@@ -5351,10 +7538,19 @@
       <c r="F243" s="1">
         <v>709.27</v>
       </c>
-    </row>
-    <row r="244" spans="1:6">
+      <c r="G243" s="1">
+        <v>723.47</v>
+      </c>
+      <c r="H243" s="1">
+        <v>1359.58</v>
+      </c>
+      <c r="I243" s="1">
+        <v>430.67</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C244" s="1">
         <v>115.03</v>
@@ -5368,27 +7564,45 @@
       <c r="F244" s="1">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="245" spans="1:6">
+      <c r="G244" s="1">
+        <v>202.16</v>
+      </c>
+      <c r="H244" s="1">
+        <v>1349.16</v>
+      </c>
+      <c r="I244" s="1">
+        <v>692.9400000000001</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C245" s="1">
-        <v>2656.319999999999</v>
+        <v>2656.32</v>
       </c>
       <c r="D245" s="1">
         <v>2226.61</v>
       </c>
       <c r="E245" s="1">
-        <v>3073.099999999999</v>
+        <v>3073.100000000001</v>
       </c>
       <c r="F245" s="1">
         <v>2590.46</v>
       </c>
-    </row>
-    <row r="246" spans="1:6">
+      <c r="G245" s="1">
+        <v>2061.1</v>
+      </c>
+      <c r="H245" s="1">
+        <v>3649.39</v>
+      </c>
+      <c r="I245" s="1">
+        <v>5084.599999999999</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C246" s="1">
         <v>336.53</v>
@@ -5402,10 +7616,19 @@
       <c r="F246" s="1">
         <v>388.3000000000001</v>
       </c>
-    </row>
-    <row r="247" spans="1:6">
+      <c r="G246" s="1">
+        <v>639.09</v>
+      </c>
+      <c r="H246" s="1">
+        <v>1276.58</v>
+      </c>
+      <c r="I246" s="1">
+        <v>955.51</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C247" s="1">
         <v>311.73</v>
@@ -5419,10 +7642,19 @@
       <c r="F247" s="1">
         <v>420.45</v>
       </c>
-    </row>
-    <row r="248" spans="1:6">
+      <c r="G247" s="1">
+        <v>758.9400000000001</v>
+      </c>
+      <c r="H247" s="1">
+        <v>1662.47</v>
+      </c>
+      <c r="I247" s="1">
+        <v>857.5500000000002</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C248" s="1">
         <v>1209.57</v>
@@ -5431,15 +7663,24 @@
         <v>1004.46</v>
       </c>
       <c r="E248" s="1">
-        <v>857.61</v>
+        <v>857.6100000000001</v>
       </c>
       <c r="F248" s="1">
-        <v>351.75</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
+        <v>351.7499999999999</v>
+      </c>
+      <c r="G248" s="1">
+        <v>523.61</v>
+      </c>
+      <c r="H248" s="1">
+        <v>2004.27</v>
+      </c>
+      <c r="I248" s="1">
+        <v>2481.5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C249" s="1">
         <v>206.1</v>
@@ -5448,15 +7689,24 @@
         <v>324.38</v>
       </c>
       <c r="E249" s="1">
-        <v>29.98999999999999</v>
+        <v>29.99</v>
       </c>
       <c r="F249" s="1">
         <v>66.99000000000001</v>
       </c>
-    </row>
-    <row r="250" spans="1:6">
+      <c r="G249" s="1">
+        <v>613.4100000000001</v>
+      </c>
+      <c r="H249" s="1">
+        <v>109.99</v>
+      </c>
+      <c r="I249" s="1">
+        <v>466.9300000000001</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C250" s="1">
         <v>1464.28</v>
@@ -5465,15 +7715,24 @@
         <v>1615.45</v>
       </c>
       <c r="E250" s="1">
-        <v>788.6199999999999</v>
+        <v>788.6200000000001</v>
       </c>
       <c r="F250" s="1">
         <v>1691.14</v>
       </c>
-    </row>
-    <row r="251" spans="1:6">
+      <c r="G250" s="1">
+        <v>1051.65</v>
+      </c>
+      <c r="H250" s="1">
+        <v>1950.75</v>
+      </c>
+      <c r="I250" s="1">
+        <v>1408.08</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C251" s="1">
         <v>408</v>
@@ -5487,16 +7746,25 @@
       <c r="F251" s="1">
         <v>84.98999999999999</v>
       </c>
-    </row>
-    <row r="252" spans="1:6">
+      <c r="G251" s="1">
+        <v>247.82</v>
+      </c>
+      <c r="H251" s="1">
+        <v>582.38</v>
+      </c>
+      <c r="I251" s="1">
+        <v>28.49000000000001</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C252" s="1">
         <v>212.89</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E252" s="1">
         <v>290.46</v>
@@ -5504,10 +7772,19 @@
       <c r="F252" s="1">
         <v>183.46</v>
       </c>
-    </row>
-    <row r="253" spans="1:6">
+      <c r="G252" s="1">
+        <v>151.96</v>
+      </c>
+      <c r="H252" s="1">
+        <v>610.08</v>
+      </c>
+      <c r="I252" s="1">
+        <v>43.98</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C253" s="1">
         <v>36.99</v>
@@ -5516,15 +7793,24 @@
         <v>124.96</v>
       </c>
       <c r="E253" s="1">
-        <v>801.8000000000002</v>
+        <v>801.8</v>
       </c>
       <c r="F253" s="1">
         <v>245.93</v>
       </c>
-    </row>
-    <row r="254" spans="1:6">
+      <c r="G253" s="1">
+        <v>56.69</v>
+      </c>
+      <c r="H253" s="1">
+        <v>542.8200000000001</v>
+      </c>
+      <c r="I253" s="1">
+        <v>455.43</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C254" s="1">
         <v>87.97</v>
@@ -5536,18 +7822,27 @@
         <v>68.47999999999999</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G254" s="1">
+        <v>225.87</v>
+      </c>
+      <c r="H254" s="1">
+        <v>338.91</v>
+      </c>
+      <c r="I254" s="1">
+        <v>440.87</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C255" s="1">
         <v>292.6</v>
       </c>
       <c r="D255" s="1">
-        <v>543.3900000000001</v>
+        <v>543.39</v>
       </c>
       <c r="E255" s="1">
         <v>925.5700000000001</v>
@@ -5555,10 +7850,19 @@
       <c r="F255" s="1">
         <v>1165.41</v>
       </c>
-    </row>
-    <row r="256" spans="1:6">
+      <c r="G255" s="1">
+        <v>707.0500000000002</v>
+      </c>
+      <c r="H255" s="1">
+        <v>1425.33</v>
+      </c>
+      <c r="I255" s="1">
+        <v>1691.25</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C256" s="1">
         <v>74.98</v>
@@ -5572,10 +7876,19 @@
       <c r="F256" s="1">
         <v>193.54</v>
       </c>
-    </row>
-    <row r="257" spans="1:6">
+      <c r="G256" s="1">
+        <v>110.97</v>
+      </c>
+      <c r="H256" s="1">
+        <v>529.76</v>
+      </c>
+      <c r="I256" s="1">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C257" s="1">
         <v>315.86</v>
@@ -5589,16 +7902,25 @@
       <c r="F257" s="1">
         <v>432.98</v>
       </c>
-    </row>
-    <row r="258" spans="1:6">
+      <c r="G257" s="1">
+        <v>292.47</v>
+      </c>
+      <c r="H257" s="1">
+        <v>1001.15</v>
+      </c>
+      <c r="I257" s="1">
+        <v>1139.64</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C258" s="1">
         <v>298.43</v>
       </c>
       <c r="D258" s="1">
-        <v>83.55999999999999</v>
+        <v>83.56</v>
       </c>
       <c r="E258" s="1">
         <v>302.95</v>
@@ -5606,10 +7928,19 @@
       <c r="F258" s="1">
         <v>74.97999999999999</v>
       </c>
-    </row>
-    <row r="259" spans="1:6">
+      <c r="G258" s="1">
+        <v>110.59</v>
+      </c>
+      <c r="H258" s="1">
+        <v>862.0799999999999</v>
+      </c>
+      <c r="I258" s="1">
+        <v>232.93</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C259" s="1">
         <v>54.98</v>
@@ -5623,13 +7954,22 @@
       <c r="F259" s="1">
         <v>190.96</v>
       </c>
-    </row>
-    <row r="260" spans="1:6">
+      <c r="G259" s="1">
+        <v>278.15</v>
+      </c>
+      <c r="H259" s="1">
+        <v>792.2600000000001</v>
+      </c>
+      <c r="I259" s="1">
+        <v>514.9400000000001</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C260" s="1">
-        <v>862.55</v>
+        <v>862.5500000000002</v>
       </c>
       <c r="D260" s="1">
         <v>470.98</v>
@@ -5640,10 +7980,19 @@
       <c r="F260" s="1">
         <v>277.08</v>
       </c>
-    </row>
-    <row r="261" spans="1:6">
+      <c r="G260" s="1">
+        <v>734.74</v>
+      </c>
+      <c r="H260" s="1">
+        <v>871.61</v>
+      </c>
+      <c r="I260" s="1">
+        <v>903.0200000000001</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C261" s="1">
         <v>159.97</v>
@@ -5657,10 +8006,19 @@
       <c r="F261" s="1">
         <v>291.14</v>
       </c>
-    </row>
-    <row r="262" spans="1:6">
+      <c r="G261" s="1">
+        <v>165.97</v>
+      </c>
+      <c r="H261" s="1">
+        <v>759.74</v>
+      </c>
+      <c r="I261" s="1">
+        <v>387.46</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C262" s="1">
         <v>317.07</v>
@@ -5674,10 +8032,19 @@
       <c r="F262" s="1">
         <v>1053.36</v>
       </c>
-    </row>
-    <row r="263" spans="1:6">
+      <c r="G262" s="1">
+        <v>1231.13</v>
+      </c>
+      <c r="H262" s="1">
+        <v>1571.65</v>
+      </c>
+      <c r="I262" s="1">
+        <v>800.05</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C263" s="1">
         <v>184.97</v>
@@ -5691,10 +8058,19 @@
       <c r="F263" s="1">
         <v>254.64</v>
       </c>
-    </row>
-    <row r="264" spans="1:6">
+      <c r="G263" s="1">
+        <v>166.47</v>
+      </c>
+      <c r="H263" s="1">
+        <v>441.55</v>
+      </c>
+      <c r="I263" s="1">
+        <v>266.31</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C264" s="1">
         <v>42.98</v>
@@ -5708,10 +8084,19 @@
       <c r="F264" s="1">
         <v>42.48999999999999</v>
       </c>
-    </row>
-    <row r="265" spans="1:6">
+      <c r="G264" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H264" s="1">
+        <v>296.46</v>
+      </c>
+      <c r="I264" s="1">
+        <v>182.97</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C265" s="1">
         <v>1197.94</v>
@@ -5720,15 +8105,24 @@
         <v>1507.98</v>
       </c>
       <c r="E265" s="1">
-        <v>942.4500000000002</v>
+        <v>942.45</v>
       </c>
       <c r="F265" s="1">
         <v>1795.67</v>
       </c>
-    </row>
-    <row r="266" spans="1:6">
+      <c r="G265" s="1">
+        <v>1161.63</v>
+      </c>
+      <c r="H265" s="1">
+        <v>3648.879999999999</v>
+      </c>
+      <c r="I265" s="1">
+        <v>2330.19</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C266" s="1">
         <v>1742.37</v>
@@ -5742,10 +8136,19 @@
       <c r="F266" s="1">
         <v>1287.01</v>
       </c>
-    </row>
-    <row r="267" spans="1:6">
+      <c r="G266" s="1">
+        <v>2378.23</v>
+      </c>
+      <c r="H266" s="1">
+        <v>2165.59</v>
+      </c>
+      <c r="I266" s="1">
+        <v>3276.309999999999</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C267" s="1">
         <v>556.2</v>
@@ -5754,18 +8157,27 @@
         <v>219.96</v>
       </c>
       <c r="E267" s="1">
-        <v>876.05</v>
+        <v>876.0500000000002</v>
       </c>
       <c r="F267" s="1">
         <v>586.5</v>
       </c>
-    </row>
-    <row r="268" spans="1:6">
+      <c r="G267" s="1">
+        <v>348.81</v>
+      </c>
+      <c r="H267" s="1">
+        <v>1708.47</v>
+      </c>
+      <c r="I267" s="1">
+        <v>1360.62</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C268" s="1">
-        <v>963.27</v>
+        <v>963.2700000000001</v>
       </c>
       <c r="D268" s="1">
         <v>602.9400000000001</v>
@@ -5776,10 +8188,19 @@
       <c r="F268" s="1">
         <v>1233.92</v>
       </c>
-    </row>
-    <row r="269" spans="1:6">
+      <c r="G268" s="1">
+        <v>383.75</v>
+      </c>
+      <c r="H268" s="1">
+        <v>892.23</v>
+      </c>
+      <c r="I268" s="1">
+        <v>421.46</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C269" s="1">
         <v>180.88</v>
@@ -5793,16 +8214,25 @@
       <c r="F269" s="1">
         <v>404.62</v>
       </c>
-    </row>
-    <row r="270" spans="1:6">
+      <c r="G269" s="1">
+        <v>449.2800000000001</v>
+      </c>
+      <c r="H269" s="1">
+        <v>227.98</v>
+      </c>
+      <c r="I269" s="1">
+        <v>805.87</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E270" s="1">
         <v>2735</v>
@@ -5810,22 +8240,40 @@
       <c r="F270" s="1">
         <v>866</v>
       </c>
-    </row>
-    <row r="271" spans="1:6">
+      <c r="G270" s="1">
+        <v>546.98</v>
+      </c>
+      <c r="H270" s="1">
+        <v>2277</v>
+      </c>
+      <c r="I270" s="1">
+        <v>4367.950000000001</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D271" s="1">
         <v>161.1</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="G271" s="1">
+        <v>91.33</v>
+      </c>
+      <c r="H271" s="1">
+        <v>411.59</v>
+      </c>
+      <c r="I271" s="1">
+        <v>4.97999999999999</v>
       </c>
     </row>
   </sheetData>
